--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_EB55400729905097278232C6EF95A49D86758229" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3610DD-062F-440A-821F-2167AB2C4203}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="11_EB55400729905097278232C6EF95A49D86758229" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C51C58BD-32B6-4554-B405-3C7E4A2DA70B}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="795" windowWidth="27510" windowHeight="14145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,6 @@
     <sheet name="Inventory" sheetId="2" r:id="rId2"/>
     <sheet name="Config" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Inventory!$A$2:$Y$114</definedName>
   </definedNames>
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="169">
   <si>
     <t>Filament Inventory — Dashboard</t>
   </si>
@@ -343,12 +340,6 @@
     <t>SL-PETG-16</t>
   </si>
   <si>
-    <t>Lavender Purple</t>
-  </si>
-  <si>
-    <t>#999999</t>
-  </si>
-  <si>
     <t>Hex is catalog placeholder (#999999 = unconfirmed), not a real swatch color</t>
   </si>
   <si>
@@ -472,9 +463,6 @@
     <t>#D6001C</t>
   </si>
   <si>
-    <t>2026-08-02T00:00:00</t>
-  </si>
-  <si>
     <t>BL-PLAB-BL</t>
   </si>
   <si>
@@ -538,7 +526,25 @@
     <t>BL-PLAB-BK</t>
   </si>
   <si>
-    <t>Depleted 2026-08-10, refil pending</t>
+    <t>Depleted 2026-08-010, refill pending</t>
+  </si>
+  <si>
+    <t>Mounted 2026-08-10</t>
+  </si>
+  <si>
+    <t>Opened 2026-08-17</t>
+  </si>
+  <si>
+    <t>Lavender Purple(Purple)</t>
+  </si>
+  <si>
+    <t>#685BC7</t>
+  </si>
+  <si>
+    <t>Depleted 8/19/26 refill pending. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+  </si>
+  <si>
+    <t>Mounted 8/19/26. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
   </si>
 </sst>
 </file>
@@ -621,7 +627,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -715,11 +721,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF999999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -780,16 +781,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0E0E0"/>
+        <fgColor rgb="FF685BC7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -823,11 +819,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB8CCE4"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8CCE4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -851,9 +865,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -934,9 +945,6 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -944,38 +952,10 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -990,26 +970,75 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF9C5700"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <b/>
@@ -1035,30 +1064,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Dashboard"/>
-      <sheetName val="Inventory"/>
-      <sheetName val="Config"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="3">
-          <cell r="B3">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1357,74 +1364,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
+      <c r="A1" s="63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="A3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="61">
         <f>SUM(Inventory!N3:N114)</f>
-        <v>62</v>
-      </c>
-      <c r="C4" s="41"/>
+        <v>63</v>
+      </c>
+      <c r="C4" s="60"/>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="62">
         <f>SUMPRODUCT(IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="41"/>
+      <c r="C5" s="60"/>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="61">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
-        <v>63</v>
-      </c>
-      <c r="C6" s="41"/>
+        <v>64</v>
+      </c>
+      <c r="C6" s="60"/>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="61">
         <f>Config!$B$3</f>
         <v>1</v>
       </c>
-      <c r="C7" s="41"/>
+      <c r="C7" s="60"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+      <c r="A9" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -1456,7 +1463,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A12,Inventory!N3:N114),0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="6">
         <f>IFERROR(SUMPRODUCT((Inventory!A3:A114=A12)*IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114)),0)</f>
@@ -1603,16 +1610,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" style="53" customWidth="1"/>
+    <col min="2" max="2" width="18" style="41" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" style="53" customWidth="1"/>
-    <col min="12" max="13" width="12" style="53" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" style="41" customWidth="1"/>
+    <col min="12" max="13" width="12" style="41" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
@@ -1622,37 +1629,37 @@
     <col min="22" max="22" width="16" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
     <col min="24" max="24" width="220.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="25" max="25" width="14" style="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="59"/>
     </row>
     <row r="2" spans="1:25" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1682,7 +1689,7 @@
       <c r="I2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="45" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -1727,7 +1734,7 @@
       <c r="X2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="54" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1755,7 +1762,7 @@
         <v>50</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="J3" s="46"/>
       <c r="K3" s="7"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -1785,14 +1792,14 @@
       <c r="V3" s="5">
         <v>0</v>
       </c>
-      <c r="W3" s="10">
+      <c r="W3" s="9">
         <f t="shared" ref="W3:W34" si="0">IF(V3="","",IF(U3="","",V3/U3))</f>
         <v>0</v>
       </c>
       <c r="X3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y3" s="9">
+      <c r="Y3" s="55">
         <f t="shared" ref="Y3:Y34" si="1">IF(OR(M3="",N3=""),0,M3*N3)</f>
         <v>0</v>
       </c>
@@ -1813,7 +1820,7 @@
       <c r="E4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="11"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="4" t="s">
         <v>58</v>
       </c>
@@ -1821,7 +1828,7 @@
         <v>50</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="J4" s="46"/>
       <c r="K4" s="7"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -1849,14 +1856,14 @@
         <v>1000</v>
       </c>
       <c r="V4" s="5">
-        <v>954</v>
-      </c>
-      <c r="W4" s="10">
+        <v>483</v>
+      </c>
+      <c r="W4" s="9">
         <f t="shared" si="0"/>
-        <v>0.95399999999999996</v>
+        <v>0.48299999999999998</v>
       </c>
       <c r="X4" s="4"/>
-      <c r="Y4" s="9">
+      <c r="Y4" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1877,7 +1884,7 @@
       <c r="E5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="4" t="s">
         <v>58</v>
       </c>
@@ -1885,7 +1892,7 @@
         <v>50</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="J5" s="46"/>
       <c r="K5" s="7"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1915,12 +1922,12 @@
       <c r="V5" s="5">
         <v>1000</v>
       </c>
-      <c r="W5" s="10">
+      <c r="W5" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X5" s="4"/>
-      <c r="Y5" s="9">
+      <c r="Y5" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1941,7 +1948,7 @@
       <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="11"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="4" t="s">
         <v>58</v>
       </c>
@@ -1949,7 +1956,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="7"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1979,12 +1986,12 @@
       <c r="V6" s="5">
         <v>1000</v>
       </c>
-      <c r="W6" s="10">
+      <c r="W6" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X6" s="4"/>
-      <c r="Y6" s="9">
+      <c r="Y6" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2005,7 +2012,7 @@
       <c r="E7" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="11"/>
       <c r="G7" s="4" t="s">
         <v>64</v>
       </c>
@@ -2013,7 +2020,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="J7" s="46"/>
       <c r="K7" s="7"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -2043,12 +2050,12 @@
       <c r="V7" s="5">
         <v>1000</v>
       </c>
-      <c r="W7" s="10">
+      <c r="W7" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X7" s="4"/>
-      <c r="Y7" s="9">
+      <c r="Y7" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2069,7 +2076,7 @@
       <c r="E8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="13"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="4" t="s">
         <v>67</v>
       </c>
@@ -2077,7 +2084,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="J8" s="46"/>
       <c r="K8" s="7"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -2107,12 +2114,12 @@
       <c r="V8" s="5">
         <v>1000</v>
       </c>
-      <c r="W8" s="10">
+      <c r="W8" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X8" s="4"/>
-      <c r="Y8" s="9">
+      <c r="Y8" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2133,7 +2140,7 @@
       <c r="E9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="12"/>
       <c r="G9" s="4" t="s">
         <v>67</v>
       </c>
@@ -2141,7 +2148,7 @@
         <v>50</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="J9" s="46"/>
       <c r="K9" s="7"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -2171,12 +2178,12 @@
       <c r="V9" s="5">
         <v>1000</v>
       </c>
-      <c r="W9" s="10">
+      <c r="W9" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X9" s="4"/>
-      <c r="Y9" s="9">
+      <c r="Y9" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2197,7 +2204,7 @@
       <c r="E10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="13"/>
       <c r="G10" s="4" t="s">
         <v>70</v>
       </c>
@@ -2205,7 +2212,7 @@
         <v>50</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="J10" s="46"/>
       <c r="K10" s="7"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -2235,12 +2242,12 @@
       <c r="V10" s="5">
         <v>939</v>
       </c>
-      <c r="W10" s="10">
+      <c r="W10" s="9">
         <f t="shared" si="0"/>
         <v>0.93899999999999995</v>
       </c>
       <c r="X10" s="4"/>
-      <c r="Y10" s="9">
+      <c r="Y10" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2261,7 +2268,7 @@
       <c r="E11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="14"/>
       <c r="G11" s="4" t="s">
         <v>73</v>
       </c>
@@ -2269,7 +2276,7 @@
         <v>50</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+      <c r="J11" s="46"/>
       <c r="K11" s="7"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -2297,14 +2304,16 @@
         <v>1000</v>
       </c>
       <c r="V11" s="5">
-        <v>123</v>
-      </c>
-      <c r="W11" s="10">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
         <f t="shared" si="0"/>
-        <v>0.123</v>
-      </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y11" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2325,7 +2334,7 @@
       <c r="E12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="16"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="4" t="s">
         <v>76</v>
       </c>
@@ -2333,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
+      <c r="J12" s="46"/>
       <c r="K12" s="7"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -2363,12 +2372,12 @@
       <c r="V12" s="5">
         <v>1000</v>
       </c>
-      <c r="W12" s="10">
+      <c r="W12" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X12" s="4"/>
-      <c r="Y12" s="9">
+      <c r="Y12" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2389,7 +2398,7 @@
       <c r="E13" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="17"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="4" t="s">
         <v>79</v>
       </c>
@@ -2397,7 +2406,7 @@
         <v>50</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="J13" s="46"/>
       <c r="K13" s="7"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -2427,14 +2436,14 @@
       <c r="V13" s="5">
         <v>0</v>
       </c>
-      <c r="W13" s="10">
+      <c r="W13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y13" s="9">
+      <c r="Y13" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2455,7 +2464,7 @@
       <c r="E14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="18"/>
+      <c r="F14" s="17"/>
       <c r="G14" s="4" t="s">
         <v>83</v>
       </c>
@@ -2463,7 +2472,7 @@
         <v>50</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="J14" s="46"/>
       <c r="K14" s="7"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -2493,12 +2502,12 @@
       <c r="V14" s="5">
         <v>1000</v>
       </c>
-      <c r="W14" s="10">
+      <c r="W14" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X14" s="4"/>
-      <c r="Y14" s="9">
+      <c r="Y14" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2519,7 +2528,7 @@
       <c r="E15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="19"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
@@ -2527,7 +2536,7 @@
         <v>50</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="J15" s="46"/>
       <c r="K15" s="7"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
@@ -2557,12 +2566,12 @@
       <c r="V15" s="5">
         <v>123</v>
       </c>
-      <c r="W15" s="10">
+      <c r="W15" s="9">
         <f t="shared" si="0"/>
         <v>0.123</v>
       </c>
       <c r="X15" s="4"/>
-      <c r="Y15" s="9">
+      <c r="Y15" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2583,7 +2592,7 @@
       <c r="E16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="20"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="4" t="s">
         <v>89</v>
       </c>
@@ -2591,7 +2600,7 @@
         <v>50</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="J16" s="46"/>
       <c r="K16" s="7"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -2621,12 +2630,12 @@
       <c r="V16" s="5">
         <v>1000</v>
       </c>
-      <c r="W16" s="10">
+      <c r="W16" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X16" s="4"/>
-      <c r="Y16" s="9">
+      <c r="Y16" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2647,7 +2656,7 @@
       <c r="E17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="4" t="s">
         <v>92</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>50</v>
       </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="J17" s="46"/>
       <c r="K17" s="7"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -2683,14 +2692,14 @@
         <v>1000</v>
       </c>
       <c r="V17" s="5">
-        <v>854</v>
-      </c>
-      <c r="W17" s="10">
+        <v>804</v>
+      </c>
+      <c r="W17" s="9">
         <f t="shared" si="0"/>
-        <v>0.85399999999999998</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="X17" s="4"/>
-      <c r="Y17" s="9">
+      <c r="Y17" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2711,7 +2720,7 @@
       <c r="E18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="22"/>
+      <c r="F18" s="21"/>
       <c r="G18" s="4" t="s">
         <v>96</v>
       </c>
@@ -2719,7 +2728,7 @@
         <v>50</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="J18" s="46"/>
       <c r="K18" s="7"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -2749,12 +2758,12 @@
       <c r="V18" s="5">
         <v>1000</v>
       </c>
-      <c r="W18" s="10">
+      <c r="W18" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X18" s="4"/>
-      <c r="Y18" s="9">
+      <c r="Y18" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2775,7 +2784,7 @@
       <c r="E19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="4" t="s">
         <v>98</v>
       </c>
@@ -2783,7 +2792,7 @@
         <v>50</v>
       </c>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
+      <c r="J19" s="46"/>
       <c r="K19" s="7"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -2798,7 +2807,7 @@
         <v>59</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>53</v>
@@ -2813,12 +2822,14 @@
       <c r="V19" s="5">
         <v>1000</v>
       </c>
-      <c r="W19" s="10">
+      <c r="W19" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="9">
+      <c r="X19" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y19" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2837,17 +2848,17 @@
         <v>47</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="4" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="53" t="s">
+        <v>166</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="J20" s="46"/>
       <c r="K20" s="7"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -2877,14 +2888,14 @@
       <c r="V20" s="5">
         <v>1000</v>
       </c>
-      <c r="W20" s="10">
+      <c r="W20" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y20" s="9">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2903,17 +2914,17 @@
         <v>47</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="4" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="F21" s="57"/>
+      <c r="G21" s="53" t="s">
+        <v>166</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="J21" s="46"/>
       <c r="K21" s="7"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -2943,14 +2954,14 @@
       <c r="V21" s="5">
         <v>1000</v>
       </c>
-      <c r="W21" s="10">
+      <c r="W21" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X21" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y21" s="9">
+        <v>100</v>
+      </c>
+      <c r="Y21" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2969,17 +2980,17 @@
         <v>47</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="4" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="F22" s="57"/>
+      <c r="G22" s="53" t="s">
+        <v>166</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="J22" s="46"/>
       <c r="K22" s="7"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -3009,14 +3020,14 @@
       <c r="V22" s="5">
         <v>1000</v>
       </c>
-      <c r="W22" s="10">
+      <c r="W22" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y22" s="9">
+        <v>100</v>
+      </c>
+      <c r="Y22" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3026,7 +3037,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>46</v>
@@ -3035,17 +3046,17 @@
         <v>47</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F23" s="23"/>
       <c r="G23" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="J23" s="46"/>
       <c r="K23" s="7"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -3075,12 +3086,12 @@
       <c r="V23" s="5">
         <v>1000</v>
       </c>
-      <c r="W23" s="10">
+      <c r="W23" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X23" s="4"/>
-      <c r="Y23" s="9">
+      <c r="Y23" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3090,7 +3101,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>46</v>
@@ -3099,17 +3110,17 @@
         <v>47</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F24" s="23"/>
       <c r="G24" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="J24" s="46"/>
       <c r="K24" s="7"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -3139,12 +3150,12 @@
       <c r="V24" s="5">
         <v>1000</v>
       </c>
-      <c r="W24" s="10">
+      <c r="W24" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X24" s="4"/>
-      <c r="Y24" s="9">
+      <c r="Y24" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3154,7 +3165,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>46</v>
@@ -3163,17 +3174,17 @@
         <v>47</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" s="26"/>
+        <v>105</v>
+      </c>
+      <c r="F25" s="24"/>
       <c r="G25" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="J25" s="46"/>
       <c r="K25" s="7"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -3201,14 +3212,14 @@
         <v>1000</v>
       </c>
       <c r="V25" s="5">
-        <v>318</v>
-      </c>
-      <c r="W25" s="10">
+        <v>165</v>
+      </c>
+      <c r="W25" s="9">
         <f t="shared" si="0"/>
-        <v>0.318</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="X25" s="4"/>
-      <c r="Y25" s="9">
+      <c r="Y25" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3218,7 +3229,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>46</v>
@@ -3227,17 +3238,17 @@
         <v>47</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="26"/>
+        <v>105</v>
+      </c>
+      <c r="F26" s="24"/>
       <c r="G26" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="J26" s="46"/>
       <c r="K26" s="7"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -3267,12 +3278,12 @@
       <c r="V26" s="5">
         <v>1000</v>
       </c>
-      <c r="W26" s="10">
+      <c r="W26" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X26" s="4"/>
-      <c r="Y26" s="9">
+      <c r="Y26" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3282,7 +3293,7 @@
         <v>18</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>46</v>
@@ -3291,17 +3302,17 @@
         <v>47</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="27"/>
+        <v>108</v>
+      </c>
+      <c r="F27" s="25"/>
       <c r="G27" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="J27" s="46"/>
       <c r="K27" s="7"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -3331,12 +3342,12 @@
       <c r="V27" s="5">
         <v>233</v>
       </c>
-      <c r="W27" s="10">
+      <c r="W27" s="9">
         <f t="shared" si="0"/>
         <v>0.23300000000000001</v>
       </c>
       <c r="X27" s="4"/>
-      <c r="Y27" s="9">
+      <c r="Y27" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3346,7 +3357,7 @@
         <v>18</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>46</v>
@@ -3355,17 +3366,17 @@
         <v>47</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="27"/>
+        <v>108</v>
+      </c>
+      <c r="F28" s="25"/>
       <c r="G28" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="J28" s="46"/>
       <c r="K28" s="7"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -3395,12 +3406,12 @@
       <c r="V28" s="5">
         <v>1000</v>
       </c>
-      <c r="W28" s="10">
+      <c r="W28" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X28" s="4"/>
-      <c r="Y28" s="9">
+      <c r="Y28" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3410,7 +3421,7 @@
         <v>18</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>46</v>
@@ -3419,17 +3430,17 @@
         <v>47</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F29" s="27"/>
+        <v>108</v>
+      </c>
+      <c r="F29" s="25"/>
       <c r="G29" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="J29" s="46"/>
       <c r="K29" s="7"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -3459,12 +3470,12 @@
       <c r="V29" s="5">
         <v>1000</v>
       </c>
-      <c r="W29" s="10">
+      <c r="W29" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X29" s="4"/>
-      <c r="Y29" s="9">
+      <c r="Y29" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3474,7 +3485,7 @@
         <v>18</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>46</v>
@@ -3483,17 +3494,17 @@
         <v>47</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" s="28"/>
+        <v>111</v>
+      </c>
+      <c r="F30" s="26"/>
       <c r="G30" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="J30" s="46"/>
       <c r="K30" s="7"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -3523,12 +3534,12 @@
       <c r="V30" s="5">
         <v>1000</v>
       </c>
-      <c r="W30" s="10">
+      <c r="W30" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X30" s="4"/>
-      <c r="Y30" s="9">
+      <c r="Y30" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3538,7 +3549,7 @@
         <v>18</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>46</v>
@@ -3547,17 +3558,17 @@
         <v>47</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F31" s="28"/>
+        <v>111</v>
+      </c>
+      <c r="F31" s="26"/>
       <c r="G31" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
+      <c r="J31" s="46"/>
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -3587,12 +3598,12 @@
       <c r="V31" s="5">
         <v>1000</v>
       </c>
-      <c r="W31" s="10">
+      <c r="W31" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X31" s="4"/>
-      <c r="Y31" s="9">
+      <c r="Y31" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3613,7 +3624,7 @@
       <c r="E32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="22"/>
       <c r="G32" s="4" t="s">
         <v>98</v>
       </c>
@@ -3621,7 +3632,7 @@
         <v>50</v>
       </c>
       <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="J32" s="46"/>
       <c r="K32" s="7"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
@@ -3651,12 +3662,12 @@
       <c r="V32" s="5">
         <v>1000</v>
       </c>
-      <c r="W32" s="10">
+      <c r="W32" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X32" s="4"/>
-      <c r="Y32" s="9">
+      <c r="Y32" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3666,7 +3677,7 @@
         <v>18</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>46</v>
@@ -3675,17 +3686,17 @@
         <v>47</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F33" s="29"/>
+        <v>114</v>
+      </c>
+      <c r="F33" s="27"/>
       <c r="G33" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="J33" s="46"/>
       <c r="K33" s="7"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -3715,12 +3726,12 @@
       <c r="V33" s="5">
         <v>1000</v>
       </c>
-      <c r="W33" s="10">
+      <c r="W33" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X33" s="4"/>
-      <c r="Y33" s="9">
+      <c r="Y33" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3730,26 +3741,26 @@
         <v>18</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="F34" s="28"/>
+      <c r="G34" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="J34" s="46"/>
       <c r="K34" s="7"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -3779,14 +3790,14 @@
       <c r="V34" s="5">
         <v>1000</v>
       </c>
-      <c r="W34" s="10">
+      <c r="W34" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="X34" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y34" s="9">
+        <v>121</v>
+      </c>
+      <c r="Y34" s="55">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3796,18 +3807,18 @@
         <v>18</v>
       </c>
       <c r="B35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="23"/>
+      <c r="F35" s="22"/>
       <c r="G35" s="4" t="s">
         <v>98</v>
       </c>
@@ -3815,7 +3826,7 @@
         <v>50</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
+      <c r="J35" s="46"/>
       <c r="K35" s="7"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6">
@@ -3847,15 +3858,15 @@
       <c r="V35" s="5">
         <v>1000</v>
       </c>
-      <c r="W35" s="10">
-        <f t="shared" ref="W35:W66" si="2">IF(V35="","",IF(U35="","",V35/U35))</f>
+      <c r="W35" s="9">
+        <f t="shared" ref="W35:W65" si="2">IF(V35="","",IF(U35="","",V35/U35))</f>
         <v>1</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y35" s="9">
-        <f t="shared" ref="Y35:Y66" si="3">IF(OR(M35="",N35=""),0,M35*N35)</f>
+        <v>125</v>
+      </c>
+      <c r="Y35" s="55">
+        <f t="shared" ref="Y35:Y65" si="3">IF(OR(M35="",N35=""),0,M35*N35)</f>
         <v>16.98</v>
       </c>
     </row>
@@ -3864,18 +3875,18 @@
         <v>18</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="23"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="4" t="s">
         <v>98</v>
       </c>
@@ -3883,7 +3894,7 @@
         <v>50</v>
       </c>
       <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
+      <c r="J36" s="46"/>
       <c r="K36" s="7"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6">
@@ -3915,14 +3926,14 @@
       <c r="V36" s="5">
         <v>1000</v>
       </c>
-      <c r="W36" s="10">
+      <c r="W36" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X36" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y36" s="9">
+        <v>125</v>
+      </c>
+      <c r="Y36" s="55">
         <f t="shared" si="3"/>
         <v>16.98</v>
       </c>
@@ -3932,26 +3943,26 @@
         <v>18</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F37" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F37" s="23"/>
       <c r="G37" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="J37" s="46"/>
       <c r="K37" s="7"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6">
@@ -3981,16 +3992,16 @@
         <v>1000</v>
       </c>
       <c r="V37" s="5">
-        <v>387</v>
-      </c>
-      <c r="W37" s="10">
+        <v>0</v>
+      </c>
+      <c r="W37" s="9">
         <f t="shared" si="2"/>
-        <v>0.38700000000000001</v>
+        <v>0</v>
       </c>
       <c r="X37" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y37" s="9">
+        <v>167</v>
+      </c>
+      <c r="Y37" s="55">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4000,26 +4011,26 @@
         <v>18</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F38" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F38" s="23"/>
       <c r="G38" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="J38" s="46"/>
       <c r="K38" s="7"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6">
@@ -4051,14 +4062,14 @@
       <c r="V38" s="5">
         <v>1000</v>
       </c>
-      <c r="W38" s="10">
+      <c r="W38" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y38" s="9">
+        <v>168</v>
+      </c>
+      <c r="Y38" s="55">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4068,26 +4079,26 @@
         <v>18</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F39" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F39" s="23"/>
       <c r="G39" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
+      <c r="J39" s="46"/>
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6">
@@ -4119,14 +4130,14 @@
       <c r="V39" s="5">
         <v>1000</v>
       </c>
-      <c r="W39" s="10">
+      <c r="W39" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y39" s="9">
+        <v>127</v>
+      </c>
+      <c r="Y39" s="55">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4136,26 +4147,26 @@
         <v>18</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F40" s="25"/>
+        <v>102</v>
+      </c>
+      <c r="F40" s="23"/>
       <c r="G40" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="J40" s="46"/>
       <c r="K40" s="7"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6">
@@ -4187,14 +4198,14 @@
       <c r="V40" s="5">
         <v>1000</v>
       </c>
-      <c r="W40" s="10">
+      <c r="W40" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y40" s="9">
+        <v>127</v>
+      </c>
+      <c r="Y40" s="55">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4204,26 +4215,26 @@
         <v>11</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" s="29"/>
+      <c r="G41" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
+      <c r="J41" s="46"/>
       <c r="K41" s="7"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -4251,14 +4262,14 @@
         <v>1000</v>
       </c>
       <c r="V41" s="5">
-        <v>940</v>
-      </c>
-      <c r="W41" s="10">
+        <v>707</v>
+      </c>
+      <c r="W41" s="9">
         <f t="shared" si="2"/>
-        <v>0.94</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="X41" s="4"/>
-      <c r="Y41" s="9">
+      <c r="Y41" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4268,7 +4279,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>56</v>
@@ -4277,9 +4288,9 @@
         <v>56</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F42" s="23"/>
+        <v>132</v>
+      </c>
+      <c r="F42" s="22"/>
       <c r="G42" s="4" t="s">
         <v>98</v>
       </c>
@@ -4287,7 +4298,7 @@
         <v>50</v>
       </c>
       <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
+      <c r="J42" s="46"/>
       <c r="K42" s="7"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -4315,14 +4326,14 @@
         <v>1000</v>
       </c>
       <c r="V42" s="5">
-        <v>304</v>
-      </c>
-      <c r="W42" s="10">
+        <v>135</v>
+      </c>
+      <c r="W42" s="9">
         <f t="shared" si="2"/>
-        <v>0.30399999999999999</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="X42" s="4"/>
-      <c r="Y42" s="9">
+      <c r="Y42" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4343,7 +4354,7 @@
       <c r="E43" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="17"/>
+      <c r="F43" s="16"/>
       <c r="G43" s="4" t="s">
         <v>79</v>
       </c>
@@ -4351,7 +4362,7 @@
         <v>50</v>
       </c>
       <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
+      <c r="J43" s="46"/>
       <c r="K43" s="7"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -4381,12 +4392,12 @@
       <c r="V43" s="5">
         <v>1000</v>
       </c>
-      <c r="W43" s="10">
+      <c r="W43" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X43" s="4"/>
-      <c r="Y43" s="9">
+      <c r="Y43" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4407,7 +4418,7 @@
       <c r="E44" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F44" s="15"/>
+      <c r="F44" s="14"/>
       <c r="G44" s="4" t="s">
         <v>73</v>
       </c>
@@ -4415,7 +4426,7 @@
         <v>50</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
+      <c r="J44" s="46"/>
       <c r="K44" s="7"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -4427,10 +4438,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R44" s="7" t="s">
         <v>53</v>
@@ -4443,14 +4454,16 @@
         <v>1000</v>
       </c>
       <c r="V44" s="5">
-        <v>1000</v>
-      </c>
-      <c r="W44" s="10">
+        <v>913</v>
+      </c>
+      <c r="W44" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="X44" s="4"/>
-      <c r="Y44" s="9">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="X44" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y44" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4460,7 +4473,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>94</v>
@@ -4469,17 +4482,17 @@
         <v>94</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F45" s="32"/>
+        <v>134</v>
+      </c>
+      <c r="F45" s="30"/>
       <c r="G45" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
+      <c r="J45" s="46"/>
       <c r="K45" s="7"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -4509,12 +4522,12 @@
       <c r="V45" s="5">
         <v>532</v>
       </c>
-      <c r="W45" s="10">
+      <c r="W45" s="9">
         <f t="shared" si="2"/>
         <v>0.53200000000000003</v>
       </c>
       <c r="X45" s="4"/>
-      <c r="Y45" s="9">
+      <c r="Y45" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4524,7 +4537,7 @@
         <v>18</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>46</v>
@@ -4533,17 +4546,17 @@
         <v>47</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F46" s="33"/>
+        <v>137</v>
+      </c>
+      <c r="F46" s="31"/>
       <c r="G46" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
+      <c r="J46" s="46"/>
       <c r="K46" s="7"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -4573,12 +4586,12 @@
       <c r="V46" s="5">
         <v>583</v>
       </c>
-      <c r="W46" s="10">
+      <c r="W46" s="9">
         <f t="shared" si="2"/>
         <v>0.58299999999999996</v>
       </c>
       <c r="X46" s="4"/>
-      <c r="Y46" s="9">
+      <c r="Y46" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4588,7 +4601,7 @@
         <v>11</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>94</v>
@@ -4599,15 +4612,15 @@
       <c r="E47" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F47" s="34"/>
+      <c r="F47" s="32"/>
       <c r="G47" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
+      <c r="J47" s="46"/>
       <c r="K47" s="7"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -4635,14 +4648,14 @@
         <v>1000</v>
       </c>
       <c r="V47" s="5">
-        <v>364</v>
-      </c>
-      <c r="W47" s="10">
+        <v>289</v>
+      </c>
+      <c r="W47" s="9">
         <f t="shared" si="2"/>
-        <v>0.36399999999999999</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="X47" s="4"/>
-      <c r="Y47" s="9">
+      <c r="Y47" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4663,7 +4676,7 @@
       <c r="E48" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="19"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="4" t="s">
         <v>86</v>
       </c>
@@ -4671,8 +4684,8 @@
         <v>50</v>
       </c>
       <c r="I48" s="4"/>
-      <c r="J48" s="4" t="s">
-        <v>143</v>
+      <c r="J48" s="46">
+        <v>46236</v>
       </c>
       <c r="K48" s="7" t="s">
         <v>11</v>
@@ -4709,12 +4722,12 @@
       <c r="V48" s="5">
         <v>1000</v>
       </c>
-      <c r="W48" s="10">
+      <c r="W48" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X48" s="4"/>
-      <c r="Y48" s="9">
+      <c r="Y48" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4735,7 +4748,7 @@
       <c r="E49" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F49" s="17"/>
+      <c r="F49" s="16"/>
       <c r="G49" s="4" t="s">
         <v>79</v>
       </c>
@@ -4743,8 +4756,8 @@
         <v>50</v>
       </c>
       <c r="I49" s="4"/>
-      <c r="J49" s="4" t="s">
-        <v>143</v>
+      <c r="J49" s="46">
+        <v>46236</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>11</v>
@@ -4781,12 +4794,12 @@
       <c r="V49" s="5">
         <v>1000</v>
       </c>
-      <c r="W49" s="10">
+      <c r="W49" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X49" s="4"/>
-      <c r="Y49" s="9">
+      <c r="Y49" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4796,27 +4809,27 @@
         <v>11</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F50" s="29"/>
+      <c r="G50" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="4" t="s">
-        <v>143</v>
+      <c r="J50" s="46">
+        <v>46236</v>
       </c>
       <c r="K50" s="7" t="s">
         <v>11</v>
@@ -4853,12 +4866,12 @@
       <c r="V50" s="5">
         <v>1000</v>
       </c>
-      <c r="W50" s="10">
+      <c r="W50" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X50" s="4"/>
-      <c r="Y50" s="9">
+      <c r="Y50" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4868,27 +4881,27 @@
         <v>11</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F51" s="29"/>
+      <c r="G51" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="4" t="s">
-        <v>143</v>
+      <c r="J51" s="46">
+        <v>46236</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>11</v>
@@ -4925,12 +4938,12 @@
       <c r="V51" s="5">
         <v>1000</v>
       </c>
-      <c r="W51" s="10">
+      <c r="W51" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X51" s="4"/>
-      <c r="Y51" s="9">
+      <c r="Y51" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4940,7 +4953,7 @@
         <v>11</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>56</v>
@@ -4949,9 +4962,9 @@
         <v>56</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F52" s="23"/>
+        <v>132</v>
+      </c>
+      <c r="F52" s="22"/>
       <c r="G52" s="4" t="s">
         <v>98</v>
       </c>
@@ -4959,8 +4972,8 @@
         <v>50</v>
       </c>
       <c r="I52" s="4"/>
-      <c r="J52" s="4" t="s">
-        <v>143</v>
+      <c r="J52" s="46">
+        <v>46236</v>
       </c>
       <c r="K52" s="7" t="s">
         <v>11</v>
@@ -4997,12 +5010,12 @@
       <c r="V52" s="5">
         <v>1000</v>
       </c>
-      <c r="W52" s="10">
+      <c r="W52" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X52" s="4"/>
-      <c r="Y52" s="9">
+      <c r="Y52" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5012,7 +5025,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>56</v>
@@ -5021,9 +5034,9 @@
         <v>56</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F53" s="23"/>
+        <v>132</v>
+      </c>
+      <c r="F53" s="22"/>
       <c r="G53" s="4" t="s">
         <v>98</v>
       </c>
@@ -5031,8 +5044,8 @@
         <v>50</v>
       </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="4" t="s">
-        <v>143</v>
+      <c r="J53" s="46">
+        <v>46236</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>11</v>
@@ -5069,12 +5082,12 @@
       <c r="V53" s="5">
         <v>1000</v>
       </c>
-      <c r="W53" s="10">
+      <c r="W53" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X53" s="4"/>
-      <c r="Y53" s="9">
+      <c r="Y53" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5095,7 +5108,7 @@
       <c r="E54" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F54" s="18"/>
+      <c r="F54" s="17"/>
       <c r="G54" s="4" t="s">
         <v>83</v>
       </c>
@@ -5103,8 +5116,8 @@
         <v>50</v>
       </c>
       <c r="I54" s="4"/>
-      <c r="J54" s="4" t="s">
-        <v>143</v>
+      <c r="J54" s="46">
+        <v>46236</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>11</v>
@@ -5141,12 +5154,12 @@
       <c r="V54" s="5">
         <v>1000</v>
       </c>
-      <c r="W54" s="10">
+      <c r="W54" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X54" s="4"/>
-      <c r="Y54" s="9">
+      <c r="Y54" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5167,7 +5180,7 @@
       <c r="E55" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="16"/>
+      <c r="F55" s="15"/>
       <c r="G55" s="4" t="s">
         <v>76</v>
       </c>
@@ -5175,8 +5188,8 @@
         <v>50</v>
       </c>
       <c r="I55" s="4"/>
-      <c r="J55" s="4" t="s">
-        <v>143</v>
+      <c r="J55" s="46">
+        <v>46236</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>11</v>
@@ -5213,12 +5226,12 @@
       <c r="V55" s="5">
         <v>1000</v>
       </c>
-      <c r="W55" s="10">
+      <c r="W55" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X55" s="4"/>
-      <c r="Y55" s="9">
+      <c r="Y55" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5239,7 +5252,7 @@
       <c r="E56" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F56" s="21"/>
+      <c r="F56" s="20"/>
       <c r="G56" s="4" t="s">
         <v>92</v>
       </c>
@@ -5247,8 +5260,8 @@
         <v>50</v>
       </c>
       <c r="I56" s="4"/>
-      <c r="J56" s="4" t="s">
-        <v>143</v>
+      <c r="J56" s="46">
+        <v>46236</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>11</v>
@@ -5285,12 +5298,12 @@
       <c r="V56" s="5">
         <v>1000</v>
       </c>
-      <c r="W56" s="10">
+      <c r="W56" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X56" s="4"/>
-      <c r="Y56" s="9">
+      <c r="Y56" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5311,7 +5324,7 @@
       <c r="E57" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F57" s="15"/>
+      <c r="F57" s="14"/>
       <c r="G57" s="4" t="s">
         <v>73</v>
       </c>
@@ -5319,8 +5332,8 @@
         <v>50</v>
       </c>
       <c r="I57" s="4"/>
-      <c r="J57" s="4" t="s">
-        <v>143</v>
+      <c r="J57" s="46">
+        <v>46236</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>11</v>
@@ -5357,12 +5370,12 @@
       <c r="V57" s="5">
         <v>1000</v>
       </c>
-      <c r="W57" s="10">
+      <c r="W57" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X57" s="4"/>
-      <c r="Y57" s="9">
+      <c r="Y57" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5383,7 +5396,7 @@
       <c r="E58" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F58" s="15"/>
+      <c r="F58" s="14"/>
       <c r="G58" s="4" t="s">
         <v>73</v>
       </c>
@@ -5391,8 +5404,8 @@
         <v>50</v>
       </c>
       <c r="I58" s="4"/>
-      <c r="J58" s="4" t="s">
-        <v>143</v>
+      <c r="J58" s="46">
+        <v>46236</v>
       </c>
       <c r="K58" s="7" t="s">
         <v>11</v>
@@ -5429,12 +5442,12 @@
       <c r="V58" s="5">
         <v>1000</v>
       </c>
-      <c r="W58" s="10">
+      <c r="W58" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X58" s="4"/>
-      <c r="Y58" s="9">
+      <c r="Y58" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5455,7 +5468,7 @@
       <c r="E59" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F59" s="14"/>
+      <c r="F59" s="13"/>
       <c r="G59" s="4" t="s">
         <v>70</v>
       </c>
@@ -5463,8 +5476,8 @@
         <v>50</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="4" t="s">
-        <v>143</v>
+      <c r="J59" s="46">
+        <v>46236</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>11</v>
@@ -5501,12 +5514,12 @@
       <c r="V59" s="5">
         <v>1000</v>
       </c>
-      <c r="W59" s="10">
+      <c r="W59" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X59" s="4"/>
-      <c r="Y59" s="9">
+      <c r="Y59" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5527,7 +5540,7 @@
       <c r="E60" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F60" s="14"/>
+      <c r="F60" s="13"/>
       <c r="G60" s="4" t="s">
         <v>70</v>
       </c>
@@ -5535,8 +5548,8 @@
         <v>50</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="4" t="s">
-        <v>143</v>
+      <c r="J60" s="46">
+        <v>46236</v>
       </c>
       <c r="K60" s="7" t="s">
         <v>11</v>
@@ -5573,12 +5586,12 @@
       <c r="V60" s="5">
         <v>1000</v>
       </c>
-      <c r="W60" s="10">
+      <c r="W60" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X60" s="4"/>
-      <c r="Y60" s="9">
+      <c r="Y60" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5588,7 +5601,7 @@
         <v>11</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>56</v>
@@ -5597,18 +5610,18 @@
         <v>56</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F61" s="35"/>
+        <v>142</v>
+      </c>
+      <c r="F61" s="33"/>
       <c r="G61" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I61" s="4"/>
-      <c r="J61" s="4" t="s">
-        <v>143</v>
+      <c r="J61" s="46">
+        <v>46236</v>
       </c>
       <c r="K61" s="7" t="s">
         <v>11</v>
@@ -5645,12 +5658,12 @@
       <c r="V61" s="5">
         <v>1000</v>
       </c>
-      <c r="W61" s="10">
+      <c r="W61" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X61" s="4"/>
-      <c r="Y61" s="9">
+      <c r="Y61" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5660,7 +5673,7 @@
         <v>11</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>56</v>
@@ -5669,18 +5682,18 @@
         <v>56</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F62" s="35"/>
+        <v>142</v>
+      </c>
+      <c r="F62" s="33"/>
       <c r="G62" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I62" s="4"/>
-      <c r="J62" s="4" t="s">
-        <v>143</v>
+      <c r="J62" s="46">
+        <v>46236</v>
       </c>
       <c r="K62" s="7" t="s">
         <v>11</v>
@@ -5717,12 +5730,12 @@
       <c r="V62" s="5">
         <v>1000</v>
       </c>
-      <c r="W62" s="10">
+      <c r="W62" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X62" s="4"/>
-      <c r="Y62" s="9">
+      <c r="Y62" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5732,7 +5745,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>56</v>
@@ -5741,18 +5754,18 @@
         <v>56</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F63" s="36"/>
+        <v>145</v>
+      </c>
+      <c r="F63" s="34"/>
       <c r="G63" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="4" t="s">
-        <v>143</v>
+      <c r="J63" s="46">
+        <v>46236</v>
       </c>
       <c r="K63" s="7" t="s">
         <v>11</v>
@@ -5789,12 +5802,12 @@
       <c r="V63" s="5">
         <v>1000</v>
       </c>
-      <c r="W63" s="10">
+      <c r="W63" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X63" s="4"/>
-      <c r="Y63" s="9">
+      <c r="Y63" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5804,7 +5817,7 @@
         <v>11</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>56</v>
@@ -5813,18 +5826,18 @@
         <v>56</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F64" s="36"/>
+        <v>145</v>
+      </c>
+      <c r="F64" s="34"/>
       <c r="G64" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I64" s="4"/>
-      <c r="J64" s="4" t="s">
-        <v>143</v>
+      <c r="J64" s="46">
+        <v>46236</v>
       </c>
       <c r="K64" s="7" t="s">
         <v>11</v>
@@ -5861,926 +5874,963 @@
       <c r="V64" s="5">
         <v>1000</v>
       </c>
-      <c r="W64" s="10">
+      <c r="W64" s="9">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="X64" s="4"/>
-      <c r="Y64" s="9">
+      <c r="Y64" s="55">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D65" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="E65" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="F65" s="49"/>
-      <c r="G65" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="H65" s="51" t="s">
+      <c r="A65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F65" s="39"/>
+      <c r="G65" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J65" s="52"/>
-      <c r="K65" s="53" t="s">
+      <c r="K65" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="N65" s="54">
+      <c r="N65" s="42">
         <v>1</v>
       </c>
       <c r="O65" s="7" t="str">
-        <f>IF(OR(N65="",[1]Config!$B$3=""),"",IF(N65&lt;=[1]Config!$B$3,"⚠ REORDER",""))</f>
+        <f>IF(OR(N64="",Config!$B$3=""),"",IF(N64&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P65" s="55" t="s">
+      <c r="P65" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="Q65" s="56" t="s">
+      <c r="Q65" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="R65" s="55" t="s">
+      <c r="R65" s="43" t="s">
         <v>53</v>
       </c>
-      <c r="T65" s="55" t="s">
+      <c r="T65" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="U65" s="54">
-        <v>1000</v>
-      </c>
-      <c r="V65" s="54">
-        <v>0</v>
-      </c>
-      <c r="W65" s="10">
+      <c r="U65" s="42">
+        <v>1000</v>
+      </c>
+      <c r="V65" s="42">
+        <v>0</v>
+      </c>
+      <c r="W65" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X65" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="Y65" s="6">
+      <c r="X65" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y65" s="55">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N66" s="37"/>
+      <c r="A66" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C66" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="F66" s="49"/>
+      <c r="G66" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="H66" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="K66" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="N66" s="50">
+        <v>1</v>
+      </c>
       <c r="O66" s="7" t="str">
-        <f>IF(OR(N66="",Config!$B$3=""),"",IF(N66&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U66" s="37"/>
-      <c r="V66" s="37"/>
-      <c r="W66" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="Y66" s="6">
-        <f t="shared" si="3"/>
+        <f>IF(OR(N64="",Config!$B$3=""),"",IF(N64&lt;=Config!$B$3,"⚠ REORDER",""))</f>
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P66" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q66" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="R66" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="T66" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="U66" s="51">
+        <v>1000</v>
+      </c>
+      <c r="V66" s="50">
+        <v>413</v>
+      </c>
+      <c r="W66" s="9">
+        <f>IF(V66="","",IF(U66="","",V66/U66))</f>
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="Y66" s="56">
+        <f>IF(OR(M65="",N65=""),0,M65*N65)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N67" s="37"/>
+      <c r="N67" s="35"/>
       <c r="O67" s="7" t="str">
         <f>IF(OR(N67="",Config!$B$3=""),"",IF(N67&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U67" s="37"/>
-      <c r="V67" s="37"/>
-      <c r="W67" s="10" t="str">
+      <c r="U67" s="35"/>
+      <c r="V67" s="35"/>
+      <c r="W67" s="9" t="str">
         <f t="shared" ref="W67:W98" si="4">IF(V67="","",IF(U67="","",V67/U67))</f>
         <v/>
       </c>
-      <c r="Y67" s="6">
+      <c r="Y67" s="55">
         <f t="shared" ref="Y67:Y98" si="5">IF(OR(M67="",N67=""),0,M67*N67)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N68" s="37"/>
+      <c r="N68" s="35"/>
       <c r="O68" s="7" t="str">
         <f>IF(OR(N68="",Config!$B$3=""),"",IF(N68&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U68" s="37"/>
-      <c r="V68" s="37"/>
-      <c r="W68" s="10" t="str">
+      <c r="U68" s="35"/>
+      <c r="V68" s="35"/>
+      <c r="W68" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y68" s="6">
+      <c r="Y68" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N69" s="37"/>
+      <c r="N69" s="35"/>
       <c r="O69" s="7" t="str">
         <f>IF(OR(N69="",Config!$B$3=""),"",IF(N69&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U69" s="37"/>
-      <c r="V69" s="37"/>
-      <c r="W69" s="10" t="str">
+      <c r="U69" s="35"/>
+      <c r="V69" s="35"/>
+      <c r="W69" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y69" s="6">
+      <c r="Y69" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N70" s="37"/>
+      <c r="N70" s="35"/>
       <c r="O70" s="7" t="str">
         <f>IF(OR(N70="",Config!$B$3=""),"",IF(N70&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U70" s="37"/>
-      <c r="V70" s="37"/>
-      <c r="W70" s="10" t="str">
+      <c r="U70" s="35"/>
+      <c r="V70" s="35"/>
+      <c r="W70" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y70" s="6">
+      <c r="Y70" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N71" s="37"/>
+      <c r="N71" s="35"/>
       <c r="O71" s="7" t="str">
         <f>IF(OR(N71="",Config!$B$3=""),"",IF(N71&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U71" s="37"/>
-      <c r="V71" s="37"/>
-      <c r="W71" s="10" t="str">
+      <c r="U71" s="35"/>
+      <c r="V71" s="35"/>
+      <c r="W71" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y71" s="6">
+      <c r="Y71" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N72" s="37"/>
+      <c r="N72" s="35"/>
       <c r="O72" s="7" t="str">
         <f>IF(OR(N72="",Config!$B$3=""),"",IF(N72&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U72" s="37"/>
-      <c r="V72" s="37"/>
-      <c r="W72" s="10" t="str">
+      <c r="U72" s="35"/>
+      <c r="V72" s="35"/>
+      <c r="W72" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y72" s="6">
+      <c r="Y72" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N73" s="37"/>
+      <c r="N73" s="35"/>
       <c r="O73" s="7" t="str">
         <f>IF(OR(N73="",Config!$B$3=""),"",IF(N73&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U73" s="37"/>
-      <c r="V73" s="37"/>
-      <c r="W73" s="10" t="str">
+      <c r="U73" s="35"/>
+      <c r="V73" s="35"/>
+      <c r="W73" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y73" s="6">
+      <c r="Y73" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N74" s="37"/>
+      <c r="N74" s="35"/>
       <c r="O74" s="7" t="str">
         <f>IF(OR(N74="",Config!$B$3=""),"",IF(N74&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U74" s="37"/>
-      <c r="V74" s="37"/>
-      <c r="W74" s="10" t="str">
+      <c r="U74" s="35"/>
+      <c r="V74" s="35"/>
+      <c r="W74" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y74" s="6">
+      <c r="Y74" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N75" s="37"/>
+      <c r="N75" s="35"/>
       <c r="O75" s="7" t="str">
         <f>IF(OR(N75="",Config!$B$3=""),"",IF(N75&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U75" s="37"/>
-      <c r="V75" s="37"/>
-      <c r="W75" s="10" t="str">
+      <c r="U75" s="35"/>
+      <c r="V75" s="35"/>
+      <c r="W75" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y75" s="6">
+      <c r="Y75" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N76" s="37"/>
+      <c r="N76" s="35"/>
       <c r="O76" s="7" t="str">
         <f>IF(OR(N76="",Config!$B$3=""),"",IF(N76&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U76" s="37"/>
-      <c r="V76" s="37"/>
-      <c r="W76" s="10" t="str">
+      <c r="U76" s="35"/>
+      <c r="V76" s="35"/>
+      <c r="W76" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y76" s="6">
+      <c r="Y76" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N77" s="37"/>
+      <c r="N77" s="35"/>
       <c r="O77" s="7" t="str">
         <f>IF(OR(N77="",Config!$B$3=""),"",IF(N77&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U77" s="37"/>
-      <c r="V77" s="37"/>
-      <c r="W77" s="10" t="str">
+      <c r="U77" s="35"/>
+      <c r="V77" s="35"/>
+      <c r="W77" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y77" s="6">
+      <c r="Y77" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N78" s="37"/>
+      <c r="N78" s="35"/>
       <c r="O78" s="7" t="str">
         <f>IF(OR(N78="",Config!$B$3=""),"",IF(N78&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U78" s="37"/>
-      <c r="V78" s="37"/>
-      <c r="W78" s="10" t="str">
+      <c r="U78" s="35"/>
+      <c r="V78" s="35"/>
+      <c r="W78" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y78" s="6">
+      <c r="Y78" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N79" s="37"/>
+      <c r="N79" s="35"/>
       <c r="O79" s="7" t="str">
         <f>IF(OR(N79="",Config!$B$3=""),"",IF(N79&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U79" s="37"/>
-      <c r="V79" s="37"/>
-      <c r="W79" s="10" t="str">
+      <c r="U79" s="35"/>
+      <c r="V79" s="35"/>
+      <c r="W79" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y79" s="6">
+      <c r="Y79" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N80" s="37"/>
+      <c r="N80" s="35"/>
       <c r="O80" s="7" t="str">
         <f>IF(OR(N80="",Config!$B$3=""),"",IF(N80&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U80" s="37"/>
-      <c r="V80" s="37"/>
-      <c r="W80" s="10" t="str">
+      <c r="U80" s="35"/>
+      <c r="V80" s="35"/>
+      <c r="W80" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y80" s="6">
+      <c r="Y80" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N81" s="37"/>
+      <c r="N81" s="35"/>
       <c r="O81" s="7" t="str">
         <f>IF(OR(N81="",Config!$B$3=""),"",IF(N81&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U81" s="37"/>
-      <c r="V81" s="37"/>
-      <c r="W81" s="10" t="str">
+      <c r="U81" s="35"/>
+      <c r="V81" s="35"/>
+      <c r="W81" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y81" s="6">
+      <c r="Y81" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N82" s="37"/>
+      <c r="N82" s="35"/>
       <c r="O82" s="7" t="str">
         <f>IF(OR(N82="",Config!$B$3=""),"",IF(N82&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U82" s="37"/>
-      <c r="V82" s="37"/>
-      <c r="W82" s="10" t="str">
+      <c r="U82" s="35"/>
+      <c r="V82" s="35"/>
+      <c r="W82" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y82" s="6">
+      <c r="Y82" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N83" s="37"/>
+      <c r="N83" s="35"/>
       <c r="O83" s="7" t="str">
         <f>IF(OR(N83="",Config!$B$3=""),"",IF(N83&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U83" s="37"/>
-      <c r="V83" s="37"/>
-      <c r="W83" s="10" t="str">
+      <c r="U83" s="35"/>
+      <c r="V83" s="35"/>
+      <c r="W83" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y83" s="6">
+      <c r="Y83" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N84" s="37"/>
+      <c r="N84" s="35"/>
       <c r="O84" s="7" t="str">
         <f>IF(OR(N84="",Config!$B$3=""),"",IF(N84&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U84" s="37"/>
-      <c r="V84" s="37"/>
-      <c r="W84" s="10" t="str">
+      <c r="U84" s="35"/>
+      <c r="V84" s="35"/>
+      <c r="W84" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y84" s="6">
+      <c r="Y84" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N85" s="37"/>
+      <c r="N85" s="35"/>
       <c r="O85" s="7" t="str">
         <f>IF(OR(N85="",Config!$B$3=""),"",IF(N85&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U85" s="37"/>
-      <c r="V85" s="37"/>
-      <c r="W85" s="10" t="str">
+      <c r="U85" s="35"/>
+      <c r="V85" s="35"/>
+      <c r="W85" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y85" s="6">
+      <c r="Y85" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N86" s="37"/>
+      <c r="N86" s="35"/>
       <c r="O86" s="7" t="str">
         <f>IF(OR(N86="",Config!$B$3=""),"",IF(N86&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U86" s="37"/>
-      <c r="V86" s="37"/>
-      <c r="W86" s="10" t="str">
+      <c r="U86" s="35"/>
+      <c r="V86" s="35"/>
+      <c r="W86" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y86" s="6">
+      <c r="Y86" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N87" s="37"/>
+      <c r="N87" s="35"/>
       <c r="O87" s="7" t="str">
         <f>IF(OR(N87="",Config!$B$3=""),"",IF(N87&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U87" s="37"/>
-      <c r="V87" s="37"/>
-      <c r="W87" s="10" t="str">
+      <c r="U87" s="35"/>
+      <c r="V87" s="35"/>
+      <c r="W87" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y87" s="6">
+      <c r="Y87" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N88" s="37"/>
+      <c r="N88" s="35"/>
       <c r="O88" s="7" t="str">
         <f>IF(OR(N88="",Config!$B$3=""),"",IF(N88&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U88" s="37"/>
-      <c r="V88" s="37"/>
-      <c r="W88" s="10" t="str">
+      <c r="U88" s="35"/>
+      <c r="V88" s="35"/>
+      <c r="W88" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y88" s="6">
+      <c r="Y88" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N89" s="37"/>
+      <c r="N89" s="35"/>
       <c r="O89" s="7" t="str">
         <f>IF(OR(N89="",Config!$B$3=""),"",IF(N89&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U89" s="37"/>
-      <c r="V89" s="37"/>
-      <c r="W89" s="10" t="str">
+      <c r="U89" s="35"/>
+      <c r="V89" s="35"/>
+      <c r="W89" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y89" s="6">
+      <c r="Y89" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N90" s="37"/>
+      <c r="N90" s="35"/>
       <c r="O90" s="7" t="str">
         <f>IF(OR(N90="",Config!$B$3=""),"",IF(N90&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U90" s="37"/>
-      <c r="V90" s="37"/>
-      <c r="W90" s="10" t="str">
+      <c r="U90" s="35"/>
+      <c r="V90" s="35"/>
+      <c r="W90" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y90" s="6">
+      <c r="Y90" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N91" s="37"/>
+      <c r="N91" s="35"/>
       <c r="O91" s="7" t="str">
         <f>IF(OR(N91="",Config!$B$3=""),"",IF(N91&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U91" s="37"/>
-      <c r="V91" s="37"/>
-      <c r="W91" s="10" t="str">
+      <c r="U91" s="35"/>
+      <c r="V91" s="35"/>
+      <c r="W91" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y91" s="6">
+      <c r="Y91" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N92" s="37"/>
+      <c r="N92" s="35"/>
       <c r="O92" s="7" t="str">
         <f>IF(OR(N92="",Config!$B$3=""),"",IF(N92&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U92" s="37"/>
-      <c r="V92" s="37"/>
-      <c r="W92" s="10" t="str">
+      <c r="U92" s="35"/>
+      <c r="V92" s="35"/>
+      <c r="W92" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y92" s="6">
+      <c r="Y92" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N93" s="37"/>
+      <c r="N93" s="35"/>
       <c r="O93" s="7" t="str">
         <f>IF(OR(N93="",Config!$B$3=""),"",IF(N93&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U93" s="37"/>
-      <c r="V93" s="37"/>
-      <c r="W93" s="10" t="str">
+      <c r="U93" s="35"/>
+      <c r="V93" s="35"/>
+      <c r="W93" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y93" s="6">
+      <c r="Y93" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N94" s="37"/>
+      <c r="N94" s="35"/>
       <c r="O94" s="7" t="str">
         <f>IF(OR(N94="",Config!$B$3=""),"",IF(N94&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U94" s="37"/>
-      <c r="V94" s="37"/>
-      <c r="W94" s="10" t="str">
+      <c r="U94" s="35"/>
+      <c r="V94" s="35"/>
+      <c r="W94" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y94" s="6">
+      <c r="Y94" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N95" s="37"/>
+      <c r="N95" s="35"/>
       <c r="O95" s="7" t="str">
         <f>IF(OR(N95="",Config!$B$3=""),"",IF(N95&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U95" s="37"/>
-      <c r="V95" s="37"/>
-      <c r="W95" s="10" t="str">
+      <c r="U95" s="35"/>
+      <c r="V95" s="35"/>
+      <c r="W95" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y95" s="6">
+      <c r="Y95" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N96" s="37"/>
+      <c r="N96" s="35"/>
       <c r="O96" s="7" t="str">
         <f>IF(OR(N96="",Config!$B$3=""),"",IF(N96&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U96" s="37"/>
-      <c r="V96" s="37"/>
-      <c r="W96" s="10" t="str">
+      <c r="U96" s="35"/>
+      <c r="V96" s="35"/>
+      <c r="W96" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y96" s="6">
+      <c r="Y96" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N97" s="37"/>
+      <c r="N97" s="35"/>
       <c r="O97" s="7" t="str">
         <f>IF(OR(N97="",Config!$B$3=""),"",IF(N97&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U97" s="37"/>
-      <c r="V97" s="37"/>
-      <c r="W97" s="10" t="str">
+      <c r="U97" s="35"/>
+      <c r="V97" s="35"/>
+      <c r="W97" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y97" s="6">
+      <c r="Y97" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N98" s="37"/>
+      <c r="N98" s="35"/>
       <c r="O98" s="7" t="str">
         <f>IF(OR(N98="",Config!$B$3=""),"",IF(N98&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U98" s="37"/>
-      <c r="V98" s="37"/>
-      <c r="W98" s="10" t="str">
+      <c r="U98" s="35"/>
+      <c r="V98" s="35"/>
+      <c r="W98" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y98" s="6">
+      <c r="Y98" s="55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N99" s="37"/>
+      <c r="N99" s="35"/>
       <c r="O99" s="7" t="str">
         <f>IF(OR(N99="",Config!$B$3=""),"",IF(N99&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U99" s="37"/>
-      <c r="V99" s="37"/>
-      <c r="W99" s="10" t="str">
-        <f t="shared" ref="W99:W130" si="6">IF(V99="","",IF(U99="","",V99/U99))</f>
-        <v/>
-      </c>
-      <c r="Y99" s="6">
+      <c r="U99" s="35"/>
+      <c r="V99" s="35"/>
+      <c r="W99" s="9" t="str">
+        <f t="shared" ref="W99:W114" si="6">IF(V99="","",IF(U99="","",V99/U99))</f>
+        <v/>
+      </c>
+      <c r="Y99" s="55">
         <f t="shared" ref="Y99:Y114" si="7">IF(OR(M99="",N99=""),0,M99*N99)</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N100" s="37"/>
+      <c r="N100" s="35"/>
       <c r="O100" s="7" t="str">
         <f>IF(OR(N100="",Config!$B$3=""),"",IF(N100&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U100" s="37"/>
-      <c r="V100" s="37"/>
-      <c r="W100" s="10" t="str">
+      <c r="U100" s="35"/>
+      <c r="V100" s="35"/>
+      <c r="W100" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y100" s="6">
+      <c r="Y100" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N101" s="37"/>
+      <c r="N101" s="35"/>
       <c r="O101" s="7" t="str">
         <f>IF(OR(N101="",Config!$B$3=""),"",IF(N101&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U101" s="37"/>
-      <c r="V101" s="37"/>
-      <c r="W101" s="10" t="str">
+      <c r="U101" s="35"/>
+      <c r="V101" s="35"/>
+      <c r="W101" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y101" s="6">
+      <c r="Y101" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N102" s="37"/>
+      <c r="N102" s="35"/>
       <c r="O102" s="7" t="str">
         <f>IF(OR(N102="",Config!$B$3=""),"",IF(N102&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U102" s="37"/>
-      <c r="V102" s="37"/>
-      <c r="W102" s="10" t="str">
+      <c r="U102" s="35"/>
+      <c r="V102" s="35"/>
+      <c r="W102" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y102" s="6">
+      <c r="Y102" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N103" s="37"/>
+      <c r="N103" s="35"/>
       <c r="O103" s="7" t="str">
         <f>IF(OR(N103="",Config!$B$3=""),"",IF(N103&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U103" s="37"/>
-      <c r="V103" s="37"/>
-      <c r="W103" s="10" t="str">
+      <c r="U103" s="35"/>
+      <c r="V103" s="35"/>
+      <c r="W103" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y103" s="6">
+      <c r="Y103" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N104" s="37"/>
+      <c r="N104" s="35"/>
       <c r="O104" s="7" t="str">
         <f>IF(OR(N104="",Config!$B$3=""),"",IF(N104&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U104" s="37"/>
-      <c r="V104" s="37"/>
-      <c r="W104" s="10" t="str">
+      <c r="U104" s="35"/>
+      <c r="V104" s="35"/>
+      <c r="W104" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y104" s="6">
+      <c r="Y104" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N105" s="37"/>
+      <c r="N105" s="35"/>
       <c r="O105" s="7" t="str">
         <f>IF(OR(N105="",Config!$B$3=""),"",IF(N105&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U105" s="37"/>
-      <c r="V105" s="37"/>
-      <c r="W105" s="10" t="str">
+      <c r="U105" s="35"/>
+      <c r="V105" s="35"/>
+      <c r="W105" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y105" s="6">
+      <c r="Y105" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N106" s="37"/>
+      <c r="N106" s="35"/>
       <c r="O106" s="7" t="str">
         <f>IF(OR(N106="",Config!$B$3=""),"",IF(N106&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U106" s="37"/>
-      <c r="V106" s="37"/>
-      <c r="W106" s="10" t="str">
+      <c r="U106" s="35"/>
+      <c r="V106" s="35"/>
+      <c r="W106" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y106" s="6">
+      <c r="Y106" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N107" s="37"/>
+      <c r="N107" s="35"/>
       <c r="O107" s="7" t="str">
         <f>IF(OR(N107="",Config!$B$3=""),"",IF(N107&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U107" s="37"/>
-      <c r="V107" s="37"/>
-      <c r="W107" s="10" t="str">
+      <c r="U107" s="35"/>
+      <c r="V107" s="35"/>
+      <c r="W107" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y107" s="6">
+      <c r="Y107" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N108" s="37"/>
+      <c r="N108" s="35"/>
       <c r="O108" s="7" t="str">
         <f>IF(OR(N108="",Config!$B$3=""),"",IF(N108&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U108" s="37"/>
-      <c r="V108" s="37"/>
-      <c r="W108" s="10" t="str">
+      <c r="U108" s="35"/>
+      <c r="V108" s="35"/>
+      <c r="W108" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y108" s="6">
+      <c r="Y108" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N109" s="37"/>
+      <c r="N109" s="35"/>
       <c r="O109" s="7" t="str">
         <f>IF(OR(N109="",Config!$B$3=""),"",IF(N109&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U109" s="37"/>
-      <c r="V109" s="37"/>
-      <c r="W109" s="10" t="str">
+      <c r="U109" s="35"/>
+      <c r="V109" s="35"/>
+      <c r="W109" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y109" s="6">
+      <c r="Y109" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N110" s="37"/>
+      <c r="N110" s="35"/>
       <c r="O110" s="7" t="str">
         <f>IF(OR(N110="",Config!$B$3=""),"",IF(N110&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U110" s="37"/>
-      <c r="V110" s="37"/>
-      <c r="W110" s="10" t="str">
+      <c r="U110" s="35"/>
+      <c r="V110" s="35"/>
+      <c r="W110" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y110" s="6">
+      <c r="Y110" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N111" s="37"/>
+      <c r="N111" s="35"/>
       <c r="O111" s="7" t="str">
         <f>IF(OR(N111="",Config!$B$3=""),"",IF(N111&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U111" s="37"/>
-      <c r="V111" s="37"/>
-      <c r="W111" s="10" t="str">
+      <c r="U111" s="35"/>
+      <c r="V111" s="35"/>
+      <c r="W111" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y111" s="6">
+      <c r="Y111" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N112" s="37"/>
+      <c r="N112" s="35"/>
       <c r="O112" s="7" t="str">
         <f>IF(OR(N112="",Config!$B$3=""),"",IF(N112&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U112" s="37"/>
-      <c r="V112" s="37"/>
-      <c r="W112" s="10" t="str">
+      <c r="U112" s="35"/>
+      <c r="V112" s="35"/>
+      <c r="W112" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y112" s="6">
+      <c r="Y112" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N113" s="37"/>
+      <c r="N113" s="35"/>
       <c r="O113" s="7" t="str">
         <f>IF(OR(N113="",Config!$B$3=""),"",IF(N113&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U113" s="37"/>
-      <c r="V113" s="37"/>
-      <c r="W113" s="10" t="str">
+      <c r="U113" s="35"/>
+      <c r="V113" s="35"/>
+      <c r="W113" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y113" s="6">
+      <c r="Y113" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N114" s="37"/>
+      <c r="N114" s="35"/>
       <c r="O114" s="7" t="str">
         <f>IF(OR(N114="",Config!$B$3=""),"",IF(N114&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U114" s="37"/>
-      <c r="V114" s="37"/>
-      <c r="W114" s="10" t="str">
+      <c r="U114" s="35"/>
+      <c r="V114" s="35"/>
+      <c r="W114" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y114" s="6">
+      <c r="Y114" s="55">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Y114" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:Y115" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Y1"/>
   </mergeCells>
-  <conditionalFormatting sqref="O3:O64 O66:O114">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="REORDER">
+  <conditionalFormatting sqref="O3:O114">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="REORDER">
       <formula>NOT(ISERROR(SEARCH("REORDER",O3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O65">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="REORDER">
-      <formula>NOT(ISERROR(SEARCH("REORDER",O65)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -6821,18 +6871,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
+      <c r="A1" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
     </row>
     <row r="2" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>44</v>
@@ -6840,46 +6890,46 @@
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="38" t="s">
-        <v>154</v>
+      <c r="C3" s="36" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>157</v>
+        <v>152</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>160</v>
+        <v>155</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>163</v>
+        <v>158</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Filament_Inventory_v6.xlsx
+++ b/Filament_Inventory_v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Desktop/Filament Master xlsx Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/399ef59fae163b27/Documents/GitHub/Unified-Filament-Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="11_EB55400729905097278232C6EF95A49D86758229" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C51C58BD-32B6-4554-B405-3C7E4A2DA70B}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="11_EB55400729905097278232C6EF95A49D86758229" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28AE94F2-5AC4-4270-BD8F-1FFDD03936D5}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="795" windowWidth="27510" windowHeight="14145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1290" yWindow="1560" windowWidth="27510" windowHeight="14145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Config" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Inventory!$A$2:$Y$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Inventory!$A$2:$Y$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="174">
   <si>
     <t>Filament Inventory — Dashboard</t>
   </si>
@@ -544,7 +544,22 @@
     <t>Depleted 8/19/26 refill pending. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
   </si>
   <si>
-    <t>Mounted 8/19/26. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+    <t>Depleted 8/23/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+  </si>
+  <si>
+    <t>Mounted 8/23/2026. Material Type corrected from "PLA 2+" — SL-PLAP2-01 belongs to the separate "PLA+ 2.0" line</t>
+  </si>
+  <si>
+    <t>Transparent</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Mounted 8/21/2026</t>
+  </si>
+  <si>
+    <t>Mounted 2026-08-21</t>
   </si>
 </sst>
 </file>
@@ -841,7 +856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -945,7 +960,6 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1032,6 +1046,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1364,74 +1387,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
+      <c r="A1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="A3" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="60">
         <f>SUM(Inventory!N3:N114)</f>
-        <v>63</v>
-      </c>
-      <c r="C4" s="60"/>
+        <v>66</v>
+      </c>
+      <c r="C4" s="59"/>
     </row>
     <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="62">
+      <c r="B5" s="61">
         <f>SUMPRODUCT(IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114))</f>
         <v>0</v>
       </c>
-      <c r="C5" s="60"/>
+      <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="60">
         <f>COUNTIF(Inventory!O3:O114,"*REORDER*")</f>
-        <v>64</v>
-      </c>
-      <c r="C6" s="60"/>
+        <v>67</v>
+      </c>
+      <c r="C6" s="59"/>
     </row>
     <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="60">
         <f>Config!$B$3</f>
         <v>1</v>
       </c>
-      <c r="C7" s="60"/>
+      <c r="C7" s="59"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
     </row>
     <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -1554,7 +1577,7 @@
       </c>
       <c r="B19" s="5">
         <f>IFERROR(SUMIF(Inventory!A3:A114,A19,Inventory!N3:N114),0)</f>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C19" s="6">
         <f>IFERROR(SUMPRODUCT((Inventory!A3:A114=A19)*IF(Inventory!M3:M114="",0,Inventory!M3:M114)*IF(Inventory!N3:N114="",0,Inventory!N3:N114)),0)</f>
@@ -1610,56 +1633,56 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18" style="41" customWidth="1"/>
+    <col min="2" max="2" width="18" style="40" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20" style="41" customWidth="1"/>
-    <col min="12" max="13" width="12" style="41" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20" style="40" customWidth="1"/>
+    <col min="12" max="13" width="12" style="40" customWidth="1"/>
+    <col min="14" max="14" width="16" style="40" customWidth="1"/>
     <col min="15" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="12" customWidth="1"/>
     <col min="18" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="21" max="21" width="14" style="40" customWidth="1"/>
+    <col min="22" max="22" width="16" style="40" customWidth="1"/>
     <col min="23" max="23" width="14" customWidth="1"/>
     <col min="24" max="24" width="220.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14" style="56" customWidth="1"/>
+    <col min="25" max="25" width="14" style="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="59"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="59"/>
+      <c r="U1" s="59"/>
+      <c r="V1" s="59"/>
+      <c r="W1" s="59"/>
+      <c r="X1" s="59"/>
+      <c r="Y1" s="58"/>
     </row>
     <row r="2" spans="1:25" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1689,7 +1712,7 @@
       <c r="I2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -1734,7 +1757,7 @@
       <c r="X2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" s="54" t="s">
+      <c r="Y2" s="53" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1762,7 +1785,7 @@
         <v>50</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="46"/>
+      <c r="J3" s="45"/>
       <c r="K3" s="7"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -1799,7 +1822,7 @@
       <c r="X3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y3" s="55">
+      <c r="Y3" s="54">
         <f t="shared" ref="Y3:Y34" si="1">IF(OR(M3="",N3=""),0,M3*N3)</f>
         <v>0</v>
       </c>
@@ -1828,7 +1851,7 @@
         <v>50</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="46"/>
+      <c r="J4" s="45"/>
       <c r="K4" s="7"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
@@ -1863,7 +1886,7 @@
         <v>0.48299999999999998</v>
       </c>
       <c r="X4" s="4"/>
-      <c r="Y4" s="55">
+      <c r="Y4" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1892,7 +1915,7 @@
         <v>50</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="46"/>
+      <c r="J5" s="45"/>
       <c r="K5" s="7"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
@@ -1927,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="X5" s="4"/>
-      <c r="Y5" s="55">
+      <c r="Y5" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1956,7 +1979,7 @@
         <v>50</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="46"/>
+      <c r="J6" s="45"/>
       <c r="K6" s="7"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -1991,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="4"/>
-      <c r="Y6" s="55">
+      <c r="Y6" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2020,7 +2043,7 @@
         <v>50</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="46"/>
+      <c r="J7" s="45"/>
       <c r="K7" s="7"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
@@ -2055,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="4"/>
-      <c r="Y7" s="55">
+      <c r="Y7" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2084,7 +2107,7 @@
         <v>50</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="46"/>
+      <c r="J8" s="45"/>
       <c r="K8" s="7"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -2119,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="X8" s="4"/>
-      <c r="Y8" s="55">
+      <c r="Y8" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2148,7 +2171,7 @@
         <v>50</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="46"/>
+      <c r="J9" s="45"/>
       <c r="K9" s="7"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -2183,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="X9" s="4"/>
-      <c r="Y9" s="55">
+      <c r="Y9" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2212,7 +2235,7 @@
         <v>50</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="46"/>
+      <c r="J10" s="45"/>
       <c r="K10" s="7"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -2247,7 +2270,7 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="X10" s="4"/>
-      <c r="Y10" s="55">
+      <c r="Y10" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2276,7 +2299,7 @@
         <v>50</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="46"/>
+      <c r="J11" s="45"/>
       <c r="K11" s="7"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -2310,10 +2333,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X11" s="47" t="s">
+      <c r="X11" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="Y11" s="55">
+      <c r="Y11" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2342,7 +2365,7 @@
         <v>50</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="46"/>
+      <c r="J12" s="45"/>
       <c r="K12" s="7"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -2377,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="X12" s="4"/>
-      <c r="Y12" s="55">
+      <c r="Y12" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2406,7 +2429,7 @@
         <v>50</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="46"/>
+      <c r="J13" s="45"/>
       <c r="K13" s="7"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -2443,7 +2466,7 @@
       <c r="X13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="Y13" s="55">
+      <c r="Y13" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2472,7 +2495,7 @@
         <v>50</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="46"/>
+      <c r="J14" s="45"/>
       <c r="K14" s="7"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -2507,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="4"/>
-      <c r="Y14" s="55">
+      <c r="Y14" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2536,7 +2559,7 @@
         <v>50</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="46"/>
+      <c r="J15" s="45"/>
       <c r="K15" s="7"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
@@ -2571,7 +2594,7 @@
         <v>0.123</v>
       </c>
       <c r="X15" s="4"/>
-      <c r="Y15" s="55">
+      <c r="Y15" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2600,7 +2623,7 @@
         <v>50</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="46"/>
+      <c r="J16" s="45"/>
       <c r="K16" s="7"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -2635,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="X16" s="4"/>
-      <c r="Y16" s="55">
+      <c r="Y16" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2664,7 +2687,7 @@
         <v>50</v>
       </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="46"/>
+      <c r="J17" s="45"/>
       <c r="K17" s="7"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -2699,7 +2722,7 @@
         <v>0.80400000000000005</v>
       </c>
       <c r="X17" s="4"/>
-      <c r="Y17" s="55">
+      <c r="Y17" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2728,7 +2751,7 @@
         <v>50</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="46"/>
+      <c r="J18" s="45"/>
       <c r="K18" s="7"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -2763,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="X18" s="4"/>
-      <c r="Y18" s="55">
+      <c r="Y18" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2792,7 +2815,7 @@
         <v>50</v>
       </c>
       <c r="I19" s="4"/>
-      <c r="J19" s="46"/>
+      <c r="J19" s="45"/>
       <c r="K19" s="7"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -2820,16 +2843,16 @@
         <v>1000</v>
       </c>
       <c r="V19" s="5">
-        <v>1000</v>
+        <v>423</v>
       </c>
       <c r="W19" s="9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="X19" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="Y19" s="55">
+      <c r="Y19" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2850,15 +2873,15 @@
       <c r="E20" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="57"/>
-      <c r="G20" s="53" t="s">
+      <c r="F20" s="56"/>
+      <c r="G20" s="52" t="s">
         <v>166</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I20" s="4"/>
-      <c r="J20" s="46"/>
+      <c r="J20" s="45"/>
       <c r="K20" s="7"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -2895,7 +2918,7 @@
       <c r="X20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Y20" s="55">
+      <c r="Y20" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2916,15 +2939,15 @@
       <c r="E21" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F21" s="57"/>
-      <c r="G21" s="53" t="s">
+      <c r="F21" s="56"/>
+      <c r="G21" s="52" t="s">
         <v>166</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="46"/>
+      <c r="J21" s="45"/>
       <c r="K21" s="7"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -2961,7 +2984,7 @@
       <c r="X21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Y21" s="55">
+      <c r="Y21" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -2982,15 +3005,15 @@
       <c r="E22" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="57"/>
-      <c r="G22" s="53" t="s">
+      <c r="F22" s="56"/>
+      <c r="G22" s="52" t="s">
         <v>166</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I22" s="4"/>
-      <c r="J22" s="46"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="7"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -3027,7 +3050,7 @@
       <c r="X22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Y22" s="55">
+      <c r="Y22" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3056,7 +3079,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="46"/>
+      <c r="J23" s="45"/>
       <c r="K23" s="7"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -3091,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="X23" s="4"/>
-      <c r="Y23" s="55">
+      <c r="Y23" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3120,7 +3143,7 @@
         <v>50</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="46"/>
+      <c r="J24" s="45"/>
       <c r="K24" s="7"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -3155,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="X24" s="4"/>
-      <c r="Y24" s="55">
+      <c r="Y24" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3184,7 +3207,7 @@
         <v>50</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="46"/>
+      <c r="J25" s="45"/>
       <c r="K25" s="7"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -3212,14 +3235,14 @@
         <v>1000</v>
       </c>
       <c r="V25" s="5">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="W25" s="9">
         <f t="shared" si="0"/>
-        <v>0.16500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="X25" s="4"/>
-      <c r="Y25" s="55">
+      <c r="Y25" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3248,7 +3271,7 @@
         <v>50</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="46"/>
+      <c r="J26" s="45"/>
       <c r="K26" s="7"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -3283,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="X26" s="4"/>
-      <c r="Y26" s="55">
+      <c r="Y26" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3312,7 +3335,7 @@
         <v>50</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="46"/>
+      <c r="J27" s="45"/>
       <c r="K27" s="7"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -3347,7 +3370,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="X27" s="4"/>
-      <c r="Y27" s="55">
+      <c r="Y27" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3376,7 +3399,7 @@
         <v>50</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="46"/>
+      <c r="J28" s="45"/>
       <c r="K28" s="7"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -3411,7 +3434,7 @@
         <v>1</v>
       </c>
       <c r="X28" s="4"/>
-      <c r="Y28" s="55">
+      <c r="Y28" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3440,7 +3463,7 @@
         <v>50</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="46"/>
+      <c r="J29" s="45"/>
       <c r="K29" s="7"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -3475,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="X29" s="4"/>
-      <c r="Y29" s="55">
+      <c r="Y29" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3504,7 +3527,7 @@
         <v>50</v>
       </c>
       <c r="I30" s="4"/>
-      <c r="J30" s="46"/>
+      <c r="J30" s="45"/>
       <c r="K30" s="7"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -3539,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="X30" s="4"/>
-      <c r="Y30" s="55">
+      <c r="Y30" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3568,7 +3591,7 @@
         <v>50</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="46"/>
+      <c r="J31" s="45"/>
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -3603,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="X31" s="4"/>
-      <c r="Y31" s="55">
+      <c r="Y31" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3632,7 +3655,7 @@
         <v>50</v>
       </c>
       <c r="I32" s="4"/>
-      <c r="J32" s="46"/>
+      <c r="J32" s="45"/>
       <c r="K32" s="7"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
@@ -3667,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="X32" s="4"/>
-      <c r="Y32" s="55">
+      <c r="Y32" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3696,7 +3719,7 @@
         <v>50</v>
       </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="46"/>
+      <c r="J33" s="45"/>
       <c r="K33" s="7"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -3731,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="X33" s="4"/>
-      <c r="Y33" s="55">
+      <c r="Y33" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3760,7 +3783,7 @@
         <v>50</v>
       </c>
       <c r="I34" s="4"/>
-      <c r="J34" s="46"/>
+      <c r="J34" s="45"/>
       <c r="K34" s="7"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -3797,7 +3820,7 @@
       <c r="X34" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="Y34" s="55">
+      <c r="Y34" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3826,7 +3849,7 @@
         <v>50</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="46"/>
+      <c r="J35" s="45"/>
       <c r="K35" s="7"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6">
@@ -3865,7 +3888,7 @@
       <c r="X35" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="Y35" s="55">
+      <c r="Y35" s="54">
         <f t="shared" ref="Y35:Y65" si="3">IF(OR(M35="",N35=""),0,M35*N35)</f>
         <v>16.98</v>
       </c>
@@ -3894,7 +3917,7 @@
         <v>50</v>
       </c>
       <c r="I36" s="4"/>
-      <c r="J36" s="46"/>
+      <c r="J36" s="45"/>
       <c r="K36" s="7"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6">
@@ -3933,7 +3956,7 @@
       <c r="X36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="Y36" s="55">
+      <c r="Y36" s="54">
         <f t="shared" si="3"/>
         <v>16.98</v>
       </c>
@@ -3962,7 +3985,7 @@
         <v>50</v>
       </c>
       <c r="I37" s="4"/>
-      <c r="J37" s="46"/>
+      <c r="J37" s="45"/>
       <c r="K37" s="7"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6">
@@ -4001,7 +4024,7 @@
       <c r="X37" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="Y37" s="55">
+      <c r="Y37" s="54">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4030,7 +4053,7 @@
         <v>50</v>
       </c>
       <c r="I38" s="4"/>
-      <c r="J38" s="46"/>
+      <c r="J38" s="45"/>
       <c r="K38" s="7"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6">
@@ -4044,10 +4067,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P38" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R38" s="7" t="s">
         <v>53</v>
@@ -4060,16 +4083,16 @@
         <v>1000</v>
       </c>
       <c r="V38" s="5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W38" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="Y38" s="55">
+      <c r="Y38" s="54">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4098,7 +4121,7 @@
         <v>50</v>
       </c>
       <c r="I39" s="4"/>
-      <c r="J39" s="46"/>
+      <c r="J39" s="45"/>
       <c r="K39" s="7"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6">
@@ -4112,10 +4135,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R39" s="7" t="s">
         <v>53</v>
@@ -4128,16 +4151,16 @@
         <v>1000</v>
       </c>
       <c r="V39" s="5">
-        <v>1000</v>
+        <v>536</v>
       </c>
       <c r="W39" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="X39" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y39" s="55">
+        <v>169</v>
+      </c>
+      <c r="Y39" s="54">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4166,7 +4189,7 @@
         <v>50</v>
       </c>
       <c r="I40" s="4"/>
-      <c r="J40" s="46"/>
+      <c r="J40" s="45"/>
       <c r="K40" s="7"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6">
@@ -4205,7 +4228,7 @@
       <c r="X40" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="Y40" s="55">
+      <c r="Y40" s="54">
         <f t="shared" si="3"/>
         <v>10.83</v>
       </c>
@@ -4234,7 +4257,7 @@
         <v>50</v>
       </c>
       <c r="I41" s="4"/>
-      <c r="J41" s="46"/>
+      <c r="J41" s="45"/>
       <c r="K41" s="7"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -4269,7 +4292,7 @@
         <v>0.70699999999999996</v>
       </c>
       <c r="X41" s="4"/>
-      <c r="Y41" s="55">
+      <c r="Y41" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4298,7 +4321,7 @@
         <v>50</v>
       </c>
       <c r="I42" s="4"/>
-      <c r="J42" s="46"/>
+      <c r="J42" s="45"/>
       <c r="K42" s="7"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -4326,14 +4349,14 @@
         <v>1000</v>
       </c>
       <c r="V42" s="5">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="W42" s="9">
         <f t="shared" si="2"/>
-        <v>0.13500000000000001</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="X42" s="4"/>
-      <c r="Y42" s="55">
+      <c r="Y42" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4362,7 +4385,7 @@
         <v>50</v>
       </c>
       <c r="I43" s="4"/>
-      <c r="J43" s="46"/>
+      <c r="J43" s="45"/>
       <c r="K43" s="7"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -4374,10 +4397,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R43" s="7" t="s">
         <v>53</v>
@@ -4390,14 +4413,16 @@
         <v>1000</v>
       </c>
       <c r="V43" s="5">
-        <v>1000</v>
+        <v>895</v>
       </c>
       <c r="W43" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="55">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="X43" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y43" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4426,7 +4451,7 @@
         <v>50</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="J44" s="46"/>
+      <c r="J44" s="45"/>
       <c r="K44" s="7"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
@@ -4460,10 +4485,10 @@
         <f t="shared" si="2"/>
         <v>0.91300000000000003</v>
       </c>
-      <c r="X44" s="47" t="s">
+      <c r="X44" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="Y44" s="55">
+      <c r="Y44" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4492,7 +4517,7 @@
         <v>50</v>
       </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="46"/>
+      <c r="J45" s="45"/>
       <c r="K45" s="7"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -4527,7 +4552,7 @@
         <v>0.53200000000000003</v>
       </c>
       <c r="X45" s="4"/>
-      <c r="Y45" s="55">
+      <c r="Y45" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4556,7 +4581,7 @@
         <v>50</v>
       </c>
       <c r="I46" s="4"/>
-      <c r="J46" s="46"/>
+      <c r="J46" s="45"/>
       <c r="K46" s="7"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -4591,7 +4616,7 @@
         <v>0.58299999999999996</v>
       </c>
       <c r="X46" s="4"/>
-      <c r="Y46" s="55">
+      <c r="Y46" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4620,7 +4645,7 @@
         <v>50</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="46"/>
+      <c r="J47" s="45"/>
       <c r="K47" s="7"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -4655,7 +4680,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="X47" s="4"/>
-      <c r="Y47" s="55">
+      <c r="Y47" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4684,7 +4709,7 @@
         <v>50</v>
       </c>
       <c r="I48" s="4"/>
-      <c r="J48" s="46">
+      <c r="J48" s="45">
         <v>46236</v>
       </c>
       <c r="K48" s="7" t="s">
@@ -4727,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="X48" s="4"/>
-      <c r="Y48" s="55">
+      <c r="Y48" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4756,7 +4781,7 @@
         <v>50</v>
       </c>
       <c r="I49" s="4"/>
-      <c r="J49" s="46">
+      <c r="J49" s="45">
         <v>46236</v>
       </c>
       <c r="K49" s="7" t="s">
@@ -4776,10 +4801,10 @@
         <v>⚠ REORDER</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="R49" s="7" t="s">
         <v>53</v>
@@ -4799,7 +4824,7 @@
         <v>1</v>
       </c>
       <c r="X49" s="4"/>
-      <c r="Y49" s="55">
+      <c r="Y49" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4828,7 +4853,7 @@
         <v>50</v>
       </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="46">
+      <c r="J50" s="45">
         <v>46236</v>
       </c>
       <c r="K50" s="7" t="s">
@@ -4871,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="X50" s="4"/>
-      <c r="Y50" s="55">
+      <c r="Y50" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4900,7 +4925,7 @@
         <v>50</v>
       </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="46">
+      <c r="J51" s="45">
         <v>46236</v>
       </c>
       <c r="K51" s="7" t="s">
@@ -4943,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="X51" s="4"/>
-      <c r="Y51" s="55">
+      <c r="Y51" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -4972,7 +4997,7 @@
         <v>50</v>
       </c>
       <c r="I52" s="4"/>
-      <c r="J52" s="46">
+      <c r="J52" s="45">
         <v>46236</v>
       </c>
       <c r="K52" s="7" t="s">
@@ -5015,7 +5040,7 @@
         <v>1</v>
       </c>
       <c r="X52" s="4"/>
-      <c r="Y52" s="55">
+      <c r="Y52" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5044,7 +5069,7 @@
         <v>50</v>
       </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="46">
+      <c r="J53" s="45">
         <v>46236</v>
       </c>
       <c r="K53" s="7" t="s">
@@ -5087,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="X53" s="4"/>
-      <c r="Y53" s="55">
+      <c r="Y53" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5116,7 +5141,7 @@
         <v>50</v>
       </c>
       <c r="I54" s="4"/>
-      <c r="J54" s="46">
+      <c r="J54" s="45">
         <v>46236</v>
       </c>
       <c r="K54" s="7" t="s">
@@ -5159,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="X54" s="4"/>
-      <c r="Y54" s="55">
+      <c r="Y54" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5188,7 +5213,7 @@
         <v>50</v>
       </c>
       <c r="I55" s="4"/>
-      <c r="J55" s="46">
+      <c r="J55" s="45">
         <v>46236</v>
       </c>
       <c r="K55" s="7" t="s">
@@ -5231,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="X55" s="4"/>
-      <c r="Y55" s="55">
+      <c r="Y55" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5260,7 +5285,7 @@
         <v>50</v>
       </c>
       <c r="I56" s="4"/>
-      <c r="J56" s="46">
+      <c r="J56" s="45">
         <v>46236</v>
       </c>
       <c r="K56" s="7" t="s">
@@ -5296,14 +5321,14 @@
         <v>1000</v>
       </c>
       <c r="V56" s="5">
-        <v>1000</v>
+        <v>739</v>
       </c>
       <c r="W56" s="9">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="X56" s="4"/>
-      <c r="Y56" s="55">
+      <c r="Y56" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5332,7 +5357,7 @@
         <v>50</v>
       </c>
       <c r="I57" s="4"/>
-      <c r="J57" s="46">
+      <c r="J57" s="45">
         <v>46236</v>
       </c>
       <c r="K57" s="7" t="s">
@@ -5375,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="X57" s="4"/>
-      <c r="Y57" s="55">
+      <c r="Y57" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5404,7 +5429,7 @@
         <v>50</v>
       </c>
       <c r="I58" s="4"/>
-      <c r="J58" s="46">
+      <c r="J58" s="45">
         <v>46236</v>
       </c>
       <c r="K58" s="7" t="s">
@@ -5447,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="X58" s="4"/>
-      <c r="Y58" s="55">
+      <c r="Y58" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5476,7 +5501,7 @@
         <v>50</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="46">
+      <c r="J59" s="45">
         <v>46236</v>
       </c>
       <c r="K59" s="7" t="s">
@@ -5519,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="X59" s="4"/>
-      <c r="Y59" s="55">
+      <c r="Y59" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5548,7 +5573,7 @@
         <v>50</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="46">
+      <c r="J60" s="45">
         <v>46236</v>
       </c>
       <c r="K60" s="7" t="s">
@@ -5591,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="X60" s="4"/>
-      <c r="Y60" s="55">
+      <c r="Y60" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5620,7 +5645,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="4"/>
-      <c r="J61" s="46">
+      <c r="J61" s="45">
         <v>46236</v>
       </c>
       <c r="K61" s="7" t="s">
@@ -5663,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="X61" s="4"/>
-      <c r="Y61" s="55">
+      <c r="Y61" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5692,7 +5717,7 @@
         <v>50</v>
       </c>
       <c r="I62" s="4"/>
-      <c r="J62" s="46">
+      <c r="J62" s="45">
         <v>46236</v>
       </c>
       <c r="K62" s="7" t="s">
@@ -5735,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="X62" s="4"/>
-      <c r="Y62" s="55">
+      <c r="Y62" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5764,7 +5789,7 @@
         <v>50</v>
       </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="46">
+      <c r="J63" s="45">
         <v>46236</v>
       </c>
       <c r="K63" s="7" t="s">
@@ -5807,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="X63" s="4"/>
-      <c r="Y63" s="55">
+      <c r="Y63" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5836,7 +5861,7 @@
         <v>50</v>
       </c>
       <c r="I64" s="4"/>
-      <c r="J64" s="46">
+      <c r="J64" s="45">
         <v>46236</v>
       </c>
       <c r="K64" s="7" t="s">
@@ -5879,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="X64" s="4"/>
-      <c r="Y64" s="55">
+      <c r="Y64" s="54">
         <f t="shared" si="3"/>
         <v>12.99</v>
       </c>
@@ -5894,931 +5919,1060 @@
       <c r="C65" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D65" s="37" t="s">
         <v>56</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F65" s="39"/>
-      <c r="G65" s="53" t="s">
+      <c r="F65" s="38"/>
+      <c r="G65" s="52" t="s">
         <v>103</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="K65" s="41" t="s">
+      <c r="K65" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N65" s="42">
+      <c r="N65" s="41">
         <v>1</v>
       </c>
       <c r="O65" s="7" t="str">
         <f>IF(OR(N64="",Config!$B$3=""),"",IF(N64&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P65" s="43" t="s">
+      <c r="P65" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="Q65" s="44" t="s">
+      <c r="Q65" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="R65" s="43" t="s">
+      <c r="R65" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="T65" s="43" t="s">
+      <c r="T65" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="U65" s="42">
-        <v>1000</v>
-      </c>
-      <c r="V65" s="42">
+      <c r="U65" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V65" s="41">
         <v>0</v>
       </c>
       <c r="W65" s="9">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X65" s="47" t="s">
+      <c r="X65" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="Y65" s="55">
+      <c r="Y65" s="54">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="48" t="s">
+      <c r="A66" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="52" t="s">
+      <c r="B66" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D66" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="E66" s="48" t="s">
+      <c r="C66" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="D66" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="F66" s="49"/>
-      <c r="G66" s="53" t="s">
+      <c r="F66" s="48"/>
+      <c r="G66" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="H66" s="44" t="s">
+      <c r="H66" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="K66" s="41" t="s">
+      <c r="K66" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="N66" s="50">
+      <c r="N66" s="49">
         <v>1</v>
       </c>
       <c r="O66" s="7" t="str">
         <f>IF(OR(N64="",Config!$B$3=""),"",IF(N64&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v>⚠ REORDER</v>
       </c>
-      <c r="P66" s="43" t="s">
+      <c r="P66" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="Q66" s="44" t="s">
+      <c r="Q66" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="R66" s="43" t="s">
+      <c r="R66" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="T66" s="43" t="s">
+      <c r="T66" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="U66" s="51">
-        <v>1000</v>
-      </c>
-      <c r="V66" s="50">
+      <c r="U66" s="50">
+        <v>1000</v>
+      </c>
+      <c r="V66" s="49">
         <v>413</v>
       </c>
       <c r="W66" s="9">
         <f>IF(V66="","",IF(U66="","",V66/U66))</f>
         <v>0.41299999999999998</v>
       </c>
-      <c r="Y66" s="56">
+      <c r="Y66" s="55">
         <f>IF(OR(M65="",N65=""),0,M65*N65)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N67" s="35"/>
+      <c r="A67" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="H67" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="J67" s="39">
+        <v>46251</v>
+      </c>
+      <c r="K67" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="L67" s="40">
+        <v>14.99</v>
+      </c>
+      <c r="M67" s="40">
+        <v>14.99</v>
+      </c>
+      <c r="N67" s="41">
+        <v>1</v>
+      </c>
       <c r="O67" s="7" t="str">
         <f>IF(OR(N67="",Config!$B$3=""),"",IF(N67&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U67" s="35"/>
-      <c r="V67" s="35"/>
-      <c r="W67" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P67" s="42" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q67" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R67" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="T67" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="U67" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V67" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W67" s="9">
         <f t="shared" ref="W67:W98" si="4">IF(V67="","",IF(U67="","",V67/U67))</f>
-        <v/>
-      </c>
-      <c r="Y67" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="54">
         <f t="shared" ref="Y67:Y98" si="5">IF(OR(M67="",N67=""),0,M67*N67)</f>
-        <v>0</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N68" s="35"/>
+      <c r="A68" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="H68" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="J68" s="39">
+        <v>46251</v>
+      </c>
+      <c r="K68" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="L68" s="40">
+        <v>14.99</v>
+      </c>
+      <c r="M68" s="40">
+        <v>14.99</v>
+      </c>
+      <c r="N68" s="41">
+        <v>1</v>
+      </c>
       <c r="O68" s="7" t="str">
         <f>IF(OR(N68="",Config!$B$3=""),"",IF(N68&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U68" s="35"/>
-      <c r="V68" s="35"/>
-      <c r="W68" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P68" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q68" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R68" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="T68" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="U68" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V68" s="41">
+        <v>1000</v>
+      </c>
+      <c r="W68" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y68" s="55">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="54">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N69" s="35"/>
+      <c r="A69" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E69" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="H69" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="N69" s="41">
+        <v>1</v>
+      </c>
       <c r="O69" s="7" t="str">
         <f>IF(OR(N69="",Config!$B$3=""),"",IF(N69&lt;=Config!$B$3,"⚠ REORDER",""))</f>
-        <v/>
-      </c>
-      <c r="U69" s="35"/>
-      <c r="V69" s="35"/>
-      <c r="W69" s="9" t="str">
+        <v>⚠ REORDER</v>
+      </c>
+      <c r="P69" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q69" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="R69" s="67" t="s">
+        <v>53</v>
+      </c>
+      <c r="T69" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="U69" s="41">
+        <v>1000</v>
+      </c>
+      <c r="V69" s="41">
+        <v>839</v>
+      </c>
+      <c r="W69" s="9">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="Y69" s="55">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="X69" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y69" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N70" s="35"/>
+      <c r="N70" s="41"/>
       <c r="O70" s="7" t="str">
         <f>IF(OR(N70="",Config!$B$3=""),"",IF(N70&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U70" s="35"/>
-      <c r="V70" s="35"/>
+      <c r="U70" s="41"/>
+      <c r="V70" s="41"/>
       <c r="W70" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y70" s="55">
+      <c r="Y70" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N71" s="35"/>
+      <c r="N71" s="41"/>
       <c r="O71" s="7" t="str">
         <f>IF(OR(N71="",Config!$B$3=""),"",IF(N71&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U71" s="35"/>
-      <c r="V71" s="35"/>
+      <c r="U71" s="41"/>
+      <c r="V71" s="41"/>
       <c r="W71" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y71" s="55">
+      <c r="Y71" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N72" s="35"/>
+      <c r="N72" s="41"/>
       <c r="O72" s="7" t="str">
         <f>IF(OR(N72="",Config!$B$3=""),"",IF(N72&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U72" s="35"/>
-      <c r="V72" s="35"/>
+      <c r="U72" s="41"/>
+      <c r="V72" s="41"/>
       <c r="W72" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y72" s="55">
+      <c r="Y72" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N73" s="35"/>
+      <c r="N73" s="41"/>
       <c r="O73" s="7" t="str">
         <f>IF(OR(N73="",Config!$B$3=""),"",IF(N73&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U73" s="35"/>
-      <c r="V73" s="35"/>
+      <c r="U73" s="41"/>
+      <c r="V73" s="41"/>
       <c r="W73" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y73" s="55">
+      <c r="Y73" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N74" s="35"/>
+      <c r="N74" s="41"/>
       <c r="O74" s="7" t="str">
         <f>IF(OR(N74="",Config!$B$3=""),"",IF(N74&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U74" s="35"/>
-      <c r="V74" s="35"/>
+      <c r="U74" s="41"/>
+      <c r="V74" s="41"/>
       <c r="W74" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y74" s="55">
+      <c r="Y74" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N75" s="35"/>
+      <c r="N75" s="41"/>
       <c r="O75" s="7" t="str">
         <f>IF(OR(N75="",Config!$B$3=""),"",IF(N75&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U75" s="35"/>
-      <c r="V75" s="35"/>
+      <c r="U75" s="41"/>
+      <c r="V75" s="41"/>
       <c r="W75" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y75" s="55">
+      <c r="Y75" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N76" s="35"/>
+      <c r="N76" s="41"/>
       <c r="O76" s="7" t="str">
         <f>IF(OR(N76="",Config!$B$3=""),"",IF(N76&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U76" s="35"/>
-      <c r="V76" s="35"/>
+      <c r="U76" s="41"/>
+      <c r="V76" s="41"/>
       <c r="W76" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y76" s="55">
+      <c r="Y76" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N77" s="35"/>
+      <c r="N77" s="41"/>
       <c r="O77" s="7" t="str">
         <f>IF(OR(N77="",Config!$B$3=""),"",IF(N77&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U77" s="35"/>
-      <c r="V77" s="35"/>
+      <c r="U77" s="41"/>
+      <c r="V77" s="41"/>
       <c r="W77" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y77" s="55">
+      <c r="Y77" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N78" s="35"/>
+      <c r="N78" s="41"/>
       <c r="O78" s="7" t="str">
         <f>IF(OR(N78="",Config!$B$3=""),"",IF(N78&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U78" s="35"/>
-      <c r="V78" s="35"/>
+      <c r="U78" s="41"/>
+      <c r="V78" s="41"/>
       <c r="W78" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y78" s="55">
+      <c r="Y78" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N79" s="35"/>
+      <c r="N79" s="41"/>
       <c r="O79" s="7" t="str">
         <f>IF(OR(N79="",Config!$B$3=""),"",IF(N79&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U79" s="35"/>
-      <c r="V79" s="35"/>
+      <c r="U79" s="41"/>
+      <c r="V79" s="41"/>
       <c r="W79" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y79" s="55">
+      <c r="Y79" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="N80" s="35"/>
+      <c r="N80" s="41"/>
       <c r="O80" s="7" t="str">
         <f>IF(OR(N80="",Config!$B$3=""),"",IF(N80&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U80" s="35"/>
-      <c r="V80" s="35"/>
+      <c r="U80" s="41"/>
+      <c r="V80" s="41"/>
       <c r="W80" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y80" s="55">
+      <c r="Y80" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N81" s="35"/>
+      <c r="N81" s="41"/>
       <c r="O81" s="7" t="str">
         <f>IF(OR(N81="",Config!$B$3=""),"",IF(N81&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U81" s="35"/>
-      <c r="V81" s="35"/>
+      <c r="U81" s="41"/>
+      <c r="V81" s="41"/>
       <c r="W81" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y81" s="55">
+      <c r="Y81" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N82" s="35"/>
+      <c r="N82" s="41"/>
       <c r="O82" s="7" t="str">
         <f>IF(OR(N82="",Config!$B$3=""),"",IF(N82&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U82" s="35"/>
-      <c r="V82" s="35"/>
+      <c r="U82" s="41"/>
+      <c r="V82" s="41"/>
       <c r="W82" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y82" s="55">
+      <c r="Y82" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N83" s="35"/>
+      <c r="N83" s="41"/>
       <c r="O83" s="7" t="str">
         <f>IF(OR(N83="",Config!$B$3=""),"",IF(N83&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U83" s="35"/>
-      <c r="V83" s="35"/>
+      <c r="U83" s="41"/>
+      <c r="V83" s="41"/>
       <c r="W83" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y83" s="55">
+      <c r="Y83" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N84" s="35"/>
+      <c r="N84" s="41"/>
       <c r="O84" s="7" t="str">
         <f>IF(OR(N84="",Config!$B$3=""),"",IF(N84&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U84" s="35"/>
-      <c r="V84" s="35"/>
+      <c r="U84" s="41"/>
+      <c r="V84" s="41"/>
       <c r="W84" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y84" s="55">
+      <c r="Y84" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N85" s="35"/>
+      <c r="N85" s="41"/>
       <c r="O85" s="7" t="str">
         <f>IF(OR(N85="",Config!$B$3=""),"",IF(N85&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U85" s="35"/>
-      <c r="V85" s="35"/>
+      <c r="U85" s="41"/>
+      <c r="V85" s="41"/>
       <c r="W85" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y85" s="55">
+      <c r="Y85" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N86" s="35"/>
+      <c r="N86" s="41"/>
       <c r="O86" s="7" t="str">
         <f>IF(OR(N86="",Config!$B$3=""),"",IF(N86&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U86" s="35"/>
-      <c r="V86" s="35"/>
+      <c r="U86" s="41"/>
+      <c r="V86" s="41"/>
       <c r="W86" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y86" s="55">
+      <c r="Y86" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N87" s="35"/>
+      <c r="N87" s="41"/>
       <c r="O87" s="7" t="str">
         <f>IF(OR(N87="",Config!$B$3=""),"",IF(N87&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U87" s="35"/>
-      <c r="V87" s="35"/>
+      <c r="U87" s="41"/>
+      <c r="V87" s="41"/>
       <c r="W87" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y87" s="55">
+      <c r="Y87" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N88" s="35"/>
+      <c r="N88" s="41"/>
       <c r="O88" s="7" t="str">
         <f>IF(OR(N88="",Config!$B$3=""),"",IF(N88&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U88" s="35"/>
-      <c r="V88" s="35"/>
+      <c r="U88" s="41"/>
+      <c r="V88" s="41"/>
       <c r="W88" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y88" s="55">
+      <c r="Y88" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N89" s="35"/>
+      <c r="N89" s="41"/>
       <c r="O89" s="7" t="str">
         <f>IF(OR(N89="",Config!$B$3=""),"",IF(N89&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U89" s="35"/>
-      <c r="V89" s="35"/>
+      <c r="U89" s="41"/>
+      <c r="V89" s="41"/>
       <c r="W89" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y89" s="55">
+      <c r="Y89" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N90" s="35"/>
+      <c r="N90" s="41"/>
       <c r="O90" s="7" t="str">
         <f>IF(OR(N90="",Config!$B$3=""),"",IF(N90&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U90" s="35"/>
-      <c r="V90" s="35"/>
+      <c r="U90" s="41"/>
+      <c r="V90" s="41"/>
       <c r="W90" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y90" s="55">
+      <c r="Y90" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N91" s="35"/>
+      <c r="N91" s="41"/>
       <c r="O91" s="7" t="str">
         <f>IF(OR(N91="",Config!$B$3=""),"",IF(N91&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U91" s="35"/>
-      <c r="V91" s="35"/>
+      <c r="U91" s="41"/>
+      <c r="V91" s="41"/>
       <c r="W91" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y91" s="55">
+      <c r="Y91" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N92" s="35"/>
+      <c r="N92" s="41"/>
       <c r="O92" s="7" t="str">
         <f>IF(OR(N92="",Config!$B$3=""),"",IF(N92&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U92" s="35"/>
-      <c r="V92" s="35"/>
+      <c r="U92" s="41"/>
+      <c r="V92" s="41"/>
       <c r="W92" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y92" s="55">
+      <c r="Y92" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N93" s="35"/>
+      <c r="N93" s="41"/>
       <c r="O93" s="7" t="str">
         <f>IF(OR(N93="",Config!$B$3=""),"",IF(N93&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U93" s="35"/>
-      <c r="V93" s="35"/>
+      <c r="U93" s="41"/>
+      <c r="V93" s="41"/>
       <c r="W93" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y93" s="55">
+      <c r="Y93" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N94" s="35"/>
+      <c r="N94" s="41"/>
       <c r="O94" s="7" t="str">
         <f>IF(OR(N94="",Config!$B$3=""),"",IF(N94&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U94" s="35"/>
-      <c r="V94" s="35"/>
+      <c r="U94" s="41"/>
+      <c r="V94" s="41"/>
       <c r="W94" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y94" s="55">
+      <c r="Y94" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N95" s="35"/>
+      <c r="N95" s="41"/>
       <c r="O95" s="7" t="str">
         <f>IF(OR(N95="",Config!$B$3=""),"",IF(N95&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U95" s="35"/>
-      <c r="V95" s="35"/>
+      <c r="U95" s="41"/>
+      <c r="V95" s="41"/>
       <c r="W95" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y95" s="55">
+      <c r="Y95" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N96" s="35"/>
+      <c r="N96" s="41"/>
       <c r="O96" s="7" t="str">
         <f>IF(OR(N96="",Config!$B$3=""),"",IF(N96&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U96" s="35"/>
-      <c r="V96" s="35"/>
+      <c r="U96" s="41"/>
+      <c r="V96" s="41"/>
       <c r="W96" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y96" s="55">
+      <c r="Y96" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N97" s="35"/>
+      <c r="N97" s="41"/>
       <c r="O97" s="7" t="str">
         <f>IF(OR(N97="",Config!$B$3=""),"",IF(N97&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U97" s="35"/>
-      <c r="V97" s="35"/>
+      <c r="U97" s="41"/>
+      <c r="V97" s="41"/>
       <c r="W97" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y97" s="55">
+      <c r="Y97" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N98" s="35"/>
+      <c r="N98" s="41"/>
       <c r="O98" s="7" t="str">
         <f>IF(OR(N98="",Config!$B$3=""),"",IF(N98&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U98" s="35"/>
-      <c r="V98" s="35"/>
+      <c r="U98" s="41"/>
+      <c r="V98" s="41"/>
       <c r="W98" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Y98" s="55">
+      <c r="Y98" s="54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N99" s="35"/>
+      <c r="N99" s="41"/>
       <c r="O99" s="7" t="str">
         <f>IF(OR(N99="",Config!$B$3=""),"",IF(N99&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U99" s="35"/>
-      <c r="V99" s="35"/>
+      <c r="U99" s="41"/>
+      <c r="V99" s="41"/>
       <c r="W99" s="9" t="str">
         <f t="shared" ref="W99:W114" si="6">IF(V99="","",IF(U99="","",V99/U99))</f>
         <v/>
       </c>
-      <c r="Y99" s="55">
+      <c r="Y99" s="54">
         <f t="shared" ref="Y99:Y114" si="7">IF(OR(M99="",N99=""),0,M99*N99)</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N100" s="35"/>
+      <c r="N100" s="41"/>
       <c r="O100" s="7" t="str">
         <f>IF(OR(N100="",Config!$B$3=""),"",IF(N100&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U100" s="35"/>
-      <c r="V100" s="35"/>
+      <c r="U100" s="41"/>
+      <c r="V100" s="41"/>
       <c r="W100" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y100" s="55">
+      <c r="Y100" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N101" s="35"/>
+      <c r="N101" s="41"/>
       <c r="O101" s="7" t="str">
         <f>IF(OR(N101="",Config!$B$3=""),"",IF(N101&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U101" s="35"/>
-      <c r="V101" s="35"/>
+      <c r="U101" s="41"/>
+      <c r="V101" s="41"/>
       <c r="W101" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y101" s="55">
+      <c r="Y101" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N102" s="35"/>
+      <c r="N102" s="41"/>
       <c r="O102" s="7" t="str">
         <f>IF(OR(N102="",Config!$B$3=""),"",IF(N102&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U102" s="35"/>
-      <c r="V102" s="35"/>
+      <c r="U102" s="41"/>
+      <c r="V102" s="41"/>
       <c r="W102" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y102" s="55">
+      <c r="Y102" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N103" s="35"/>
+      <c r="N103" s="41"/>
       <c r="O103" s="7" t="str">
         <f>IF(OR(N103="",Config!$B$3=""),"",IF(N103&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U103" s="35"/>
-      <c r="V103" s="35"/>
+      <c r="U103" s="41"/>
+      <c r="V103" s="41"/>
       <c r="W103" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y103" s="55">
+      <c r="Y103" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="104" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N104" s="35"/>
+      <c r="N104" s="41"/>
       <c r="O104" s="7" t="str">
         <f>IF(OR(N104="",Config!$B$3=""),"",IF(N104&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U104" s="35"/>
-      <c r="V104" s="35"/>
+      <c r="U104" s="41"/>
+      <c r="V104" s="41"/>
       <c r="W104" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y104" s="55">
+      <c r="Y104" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N105" s="35"/>
+      <c r="N105" s="41"/>
       <c r="O105" s="7" t="str">
         <f>IF(OR(N105="",Config!$B$3=""),"",IF(N105&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U105" s="35"/>
-      <c r="V105" s="35"/>
+      <c r="U105" s="41"/>
+      <c r="V105" s="41"/>
       <c r="W105" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y105" s="55">
+      <c r="Y105" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N106" s="35"/>
+      <c r="N106" s="41"/>
       <c r="O106" s="7" t="str">
         <f>IF(OR(N106="",Config!$B$3=""),"",IF(N106&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U106" s="35"/>
-      <c r="V106" s="35"/>
+      <c r="U106" s="41"/>
+      <c r="V106" s="41"/>
       <c r="W106" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y106" s="55">
+      <c r="Y106" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N107" s="35"/>
+      <c r="N107" s="41"/>
       <c r="O107" s="7" t="str">
         <f>IF(OR(N107="",Config!$B$3=""),"",IF(N107&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U107" s="35"/>
-      <c r="V107" s="35"/>
+      <c r="U107" s="41"/>
+      <c r="V107" s="41"/>
       <c r="W107" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y107" s="55">
+      <c r="Y107" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N108" s="35"/>
+      <c r="N108" s="41"/>
       <c r="O108" s="7" t="str">
         <f>IF(OR(N108="",Config!$B$3=""),"",IF(N108&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U108" s="35"/>
-      <c r="V108" s="35"/>
+      <c r="U108" s="41"/>
+      <c r="V108" s="41"/>
       <c r="W108" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y108" s="55">
+      <c r="Y108" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N109" s="35"/>
+      <c r="N109" s="41"/>
       <c r="O109" s="7" t="str">
         <f>IF(OR(N109="",Config!$B$3=""),"",IF(N109&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U109" s="35"/>
-      <c r="V109" s="35"/>
+      <c r="U109" s="41"/>
+      <c r="V109" s="41"/>
       <c r="W109" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y109" s="55">
+      <c r="Y109" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N110" s="35"/>
+      <c r="N110" s="41"/>
       <c r="O110" s="7" t="str">
         <f>IF(OR(N110="",Config!$B$3=""),"",IF(N110&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U110" s="35"/>
-      <c r="V110" s="35"/>
+      <c r="U110" s="41"/>
+      <c r="V110" s="41"/>
       <c r="W110" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y110" s="55">
+      <c r="Y110" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N111" s="35"/>
+      <c r="N111" s="41"/>
       <c r="O111" s="7" t="str">
         <f>IF(OR(N111="",Config!$B$3=""),"",IF(N111&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U111" s="35"/>
-      <c r="V111" s="35"/>
+      <c r="U111" s="41"/>
+      <c r="V111" s="41"/>
       <c r="W111" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y111" s="55">
+      <c r="Y111" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N112" s="35"/>
+      <c r="N112" s="41"/>
       <c r="O112" s="7" t="str">
         <f>IF(OR(N112="",Config!$B$3=""),"",IF(N112&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U112" s="35"/>
-      <c r="V112" s="35"/>
+      <c r="U112" s="41"/>
+      <c r="V112" s="41"/>
       <c r="W112" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y112" s="55">
+      <c r="Y112" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N113" s="35"/>
+      <c r="N113" s="41"/>
       <c r="O113" s="7" t="str">
         <f>IF(OR(N113="",Config!$B$3=""),"",IF(N113&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U113" s="35"/>
-      <c r="V113" s="35"/>
+      <c r="U113" s="41"/>
+      <c r="V113" s="41"/>
       <c r="W113" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y113" s="55">
+      <c r="Y113" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="14:25" x14ac:dyDescent="0.25">
-      <c r="N114" s="35"/>
+      <c r="N114" s="41"/>
       <c r="O114" s="7" t="str">
         <f>IF(OR(N114="",Config!$B$3=""),"",IF(N114&lt;=Config!$B$3,"⚠ REORDER",""))</f>
         <v/>
       </c>
-      <c r="U114" s="35"/>
-      <c r="V114" s="35"/>
+      <c r="U114" s="41"/>
+      <c r="V114" s="41"/>
       <c r="W114" s="9" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Y114" s="55">
+      <c r="Y114" s="54">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -6871,11 +7025,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
     </row>
     <row r="2" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -6895,7 +7049,7 @@
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="35" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6903,10 +7057,10 @@
       <c r="A4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>154</v>
       </c>
     </row>
@@ -6914,10 +7068,10 @@
       <c r="A5" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="35" t="s">
         <v>157</v>
       </c>
     </row>
@@ -6925,10 +7079,10 @@
       <c r="A6" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="35" t="s">
         <v>160</v>
       </c>
     </row>
